--- a/research/traditional_assets/database/data/zimbabwe/zimbabwe_beverage_alcoholic.xlsx
+++ b/research/traditional_assets/database/data/zimbabwe/zimbabwe_beverage_alcoholic.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1587997630207021</v>
+        <v>0.1582732138501297</v>
       </c>
       <c r="C2">
-        <v>84.65186143155931</v>
+        <v>83.86562551400799</v>
       </c>
       <c r="D2">
-        <v>66.95186143155931</v>
+        <v>67.00862551400799</v>
       </c>
       <c r="E2">
-        <v>-27.2</v>
+        <v>-26.357</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.843</v>
       </c>
       <c r="G2">
         <v>17.7</v>
@@ -1451,28 +1451,28 @@
         <v>154.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.04240289999999999</v>
       </c>
       <c r="N2">
-        <v>154.1</v>
+        <v>154.0575971</v>
       </c>
       <c r="O2">
-        <v>53.935</v>
+        <v>53.92015898499999</v>
       </c>
       <c r="P2">
-        <v>100.165</v>
+        <v>100.137438115</v>
       </c>
       <c r="Q2">
-        <v>114.765</v>
+        <v>114.737438115</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1587997630207021</v>
+        <v>0.1595416806566966</v>
       </c>
       <c r="T2">
-        <v>0.6910924838905985</v>
+        <v>0.6956299597949308</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>3634.185397696856</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1582732138501297</v>
+        <v>0.1577466646795572</v>
       </c>
       <c r="C3">
-        <v>83.86562551400799</v>
+        <v>83.07948593120116</v>
       </c>
       <c r="D3">
-        <v>67.00862551400799</v>
+        <v>67.06548593120115</v>
       </c>
       <c r="E3">
-        <v>-26.357</v>
+        <v>-25.514</v>
       </c>
       <c r="F3">
-        <v>0.843</v>
+        <v>1.686</v>
       </c>
       <c r="G3">
         <v>17.7</v>
@@ -1533,28 +1533,28 @@
         <v>154.1</v>
       </c>
       <c r="M3">
-        <v>0.04240289999999999</v>
+        <v>0.08480579999999999</v>
       </c>
       <c r="N3">
-        <v>154.0575971</v>
+        <v>154.0151942</v>
       </c>
       <c r="O3">
-        <v>53.92015898499999</v>
+        <v>53.90531797</v>
       </c>
       <c r="P3">
-        <v>100.137438115</v>
+        <v>100.10987623</v>
       </c>
       <c r="Q3">
-        <v>114.737438115</v>
+        <v>114.70987623</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1595416806566966</v>
+        <v>0.1602987394689359</v>
       </c>
       <c r="T3">
-        <v>0.6956299597949308</v>
+        <v>0.700260037248331</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>3634.185397696856</v>
+        <v>1817.092698848428</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1577466646795572</v>
+        <v>0.1572201155089847</v>
       </c>
       <c r="C4">
-        <v>83.07948593120116</v>
+        <v>82.29344292858275</v>
       </c>
       <c r="D4">
-        <v>67.06548593120115</v>
+        <v>67.12244292858274</v>
       </c>
       <c r="E4">
-        <v>-25.514</v>
+        <v>-24.671</v>
       </c>
       <c r="F4">
-        <v>1.686</v>
+        <v>2.529</v>
       </c>
       <c r="G4">
         <v>17.7</v>
@@ -1615,28 +1615,28 @@
         <v>154.1</v>
       </c>
       <c r="M4">
-        <v>0.08480579999999999</v>
+        <v>0.1272087</v>
       </c>
       <c r="N4">
-        <v>154.0151942</v>
+        <v>153.9727913</v>
       </c>
       <c r="O4">
-        <v>53.90531797</v>
+        <v>53.89047695499999</v>
       </c>
       <c r="P4">
-        <v>100.10987623</v>
+        <v>100.082314345</v>
       </c>
       <c r="Q4">
-        <v>114.70987623</v>
+        <v>114.682314345</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1602987394689359</v>
+        <v>0.1610714077412214</v>
       </c>
       <c r="T4">
-        <v>0.700260037248331</v>
+        <v>0.7049855802162343</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>1817.092698848428</v>
+        <v>1211.395132565618</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1572201155089847</v>
+        <v>0.1566935663384123</v>
       </c>
       <c r="C5">
-        <v>82.29344292858275</v>
+        <v>81.50749675243112</v>
       </c>
       <c r="D5">
-        <v>67.12244292858274</v>
+        <v>67.17949675243112</v>
       </c>
       <c r="E5">
-        <v>-24.671</v>
+        <v>-23.828</v>
       </c>
       <c r="F5">
-        <v>2.529</v>
+        <v>3.372</v>
       </c>
       <c r="G5">
         <v>17.7</v>
@@ -1697,28 +1697,28 @@
         <v>154.1</v>
       </c>
       <c r="M5">
-        <v>0.1272087</v>
+        <v>0.1696116</v>
       </c>
       <c r="N5">
-        <v>153.9727913</v>
+        <v>153.9303884</v>
       </c>
       <c r="O5">
-        <v>53.89047695499999</v>
+        <v>53.87563594</v>
       </c>
       <c r="P5">
-        <v>100.082314345</v>
+        <v>100.05475246</v>
       </c>
       <c r="Q5">
-        <v>114.682314345</v>
+        <v>114.65475246</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1610714077412214</v>
+        <v>0.1618601732691795</v>
       </c>
       <c r="T5">
-        <v>0.7049855802162343</v>
+        <v>0.7098095719959689</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>1211.395132565618</v>
+        <v>908.546349424214</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1566935663384123</v>
+        <v>0.1561670171678398</v>
       </c>
       <c r="C6">
-        <v>81.50749675243112</v>
+        <v>80.72164764986273</v>
       </c>
       <c r="D6">
-        <v>67.17949675243112</v>
+        <v>67.23664764986273</v>
       </c>
       <c r="E6">
-        <v>-23.828</v>
+        <v>-22.985</v>
       </c>
       <c r="F6">
-        <v>3.372</v>
+        <v>4.215</v>
       </c>
       <c r="G6">
         <v>17.7</v>
@@ -1779,28 +1779,28 @@
         <v>154.1</v>
       </c>
       <c r="M6">
-        <v>0.1696116</v>
+        <v>0.2120145</v>
       </c>
       <c r="N6">
-        <v>153.9303884</v>
+        <v>153.8879855</v>
       </c>
       <c r="O6">
-        <v>53.87563594</v>
+        <v>53.86079492499999</v>
       </c>
       <c r="P6">
-        <v>100.05475246</v>
+        <v>100.027190575</v>
       </c>
       <c r="Q6">
-        <v>114.65475246</v>
+        <v>114.627190575</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1618601732691795</v>
+        <v>0.1626655443871998</v>
       </c>
       <c r="T6">
-        <v>0.7098095719959689</v>
+        <v>0.7147351214973822</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>908.546349424214</v>
+        <v>726.8370795393711</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1561670171678398</v>
+        <v>0.1556404679972674</v>
       </c>
       <c r="C7">
-        <v>80.72164764986273</v>
+        <v>79.93589586883564</v>
       </c>
       <c r="D7">
-        <v>67.23664764986273</v>
+        <v>67.29389586883563</v>
       </c>
       <c r="E7">
-        <v>-22.985</v>
+        <v>-22.142</v>
       </c>
       <c r="F7">
-        <v>4.215</v>
+        <v>5.058</v>
       </c>
       <c r="G7">
         <v>17.7</v>
@@ -1861,28 +1861,28 @@
         <v>154.1</v>
       </c>
       <c r="M7">
-        <v>0.2120145</v>
+        <v>0.2544174</v>
       </c>
       <c r="N7">
-        <v>153.8879855</v>
+        <v>153.8455826</v>
       </c>
       <c r="O7">
-        <v>53.86079492499999</v>
+        <v>53.84595391</v>
       </c>
       <c r="P7">
-        <v>100.027190575</v>
+        <v>99.99962869000001</v>
       </c>
       <c r="Q7">
-        <v>114.627190575</v>
+        <v>114.59962869</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1626655443871998</v>
+        <v>0.1634880510609227</v>
       </c>
       <c r="T7">
-        <v>0.7147351214973822</v>
+        <v>0.7197654699243574</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>726.8370795393711</v>
+        <v>605.6975662828094</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1556404679972674</v>
+        <v>0.1551139188266949</v>
       </c>
       <c r="C8">
-        <v>79.93589586883564</v>
+        <v>79.15024165815312</v>
       </c>
       <c r="D8">
-        <v>67.29389586883563</v>
+        <v>67.35124165815311</v>
       </c>
       <c r="E8">
-        <v>-22.142</v>
+        <v>-21.299</v>
       </c>
       <c r="F8">
-        <v>5.058</v>
+        <v>5.900999999999999</v>
       </c>
       <c r="G8">
         <v>17.7</v>
@@ -1943,28 +1943,28 @@
         <v>154.1</v>
       </c>
       <c r="M8">
-        <v>0.2544174</v>
+        <v>0.2968202999999999</v>
       </c>
       <c r="N8">
-        <v>153.8455826</v>
+        <v>153.8031797</v>
       </c>
       <c r="O8">
-        <v>53.84595391</v>
+        <v>53.83111289499999</v>
       </c>
       <c r="P8">
-        <v>99.99962869000001</v>
+        <v>99.972066805</v>
       </c>
       <c r="Q8">
-        <v>114.59962869</v>
+        <v>114.572066805</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1634880510609227</v>
+        <v>0.1643282460502096</v>
       </c>
       <c r="T8">
-        <v>0.7197654699243574</v>
+        <v>0.7249039978873966</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>605.6975662828094</v>
+        <v>519.1693425281223</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1551139188266949</v>
+        <v>0.1545873696561225</v>
       </c>
       <c r="C9">
-        <v>79.15024165815313</v>
+        <v>78.36468526746729</v>
       </c>
       <c r="D9">
-        <v>67.35124165815313</v>
+        <v>67.40868526746729</v>
       </c>
       <c r="E9">
-        <v>-21.299</v>
+        <v>-20.456</v>
       </c>
       <c r="F9">
-        <v>5.901000000000001</v>
+        <v>6.744</v>
       </c>
       <c r="G9">
         <v>17.7</v>
@@ -2025,28 +2025,28 @@
         <v>154.1</v>
       </c>
       <c r="M9">
-        <v>0.2968203</v>
+        <v>0.3392231999999999</v>
       </c>
       <c r="N9">
-        <v>153.8031797</v>
+        <v>153.7607768</v>
       </c>
       <c r="O9">
-        <v>53.83111289499999</v>
+        <v>53.81627188</v>
       </c>
       <c r="P9">
-        <v>99.972066805</v>
+        <v>99.94450492000001</v>
       </c>
       <c r="Q9">
-        <v>114.572066805</v>
+        <v>114.54450492</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1643282460502096</v>
+        <v>0.1651867061479592</v>
       </c>
       <c r="T9">
-        <v>0.7249039978873966</v>
+        <v>0.7301542329800671</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>519.1693425281221</v>
+        <v>454.273174712107</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1545873696561225</v>
+        <v>0.15406082048555</v>
       </c>
       <c r="C10">
-        <v>78.36468526746729</v>
+        <v>77.57922694728265</v>
       </c>
       <c r="D10">
-        <v>67.40868526746729</v>
+        <v>67.46622694728265</v>
       </c>
       <c r="E10">
-        <v>-20.456</v>
+        <v>-19.613</v>
       </c>
       <c r="F10">
-        <v>6.744</v>
+        <v>7.587</v>
       </c>
       <c r="G10">
         <v>17.7</v>
@@ -2107,28 +2107,28 @@
         <v>154.1</v>
       </c>
       <c r="M10">
-        <v>0.3392231999999999</v>
+        <v>0.3816261</v>
       </c>
       <c r="N10">
-        <v>153.7607768</v>
+        <v>153.7183739</v>
       </c>
       <c r="O10">
-        <v>53.81627188</v>
+        <v>53.80143086499999</v>
       </c>
       <c r="P10">
-        <v>99.94450492000001</v>
+        <v>99.916943035</v>
       </c>
       <c r="Q10">
-        <v>114.54450492</v>
+        <v>114.516943035</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1651867061479592</v>
+        <v>0.1660640335006044</v>
       </c>
       <c r="T10">
-        <v>0.7301542329800671</v>
+        <v>0.7355198578549942</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>454.273174712107</v>
+        <v>403.7983775218729</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.15406082048555</v>
+        <v>0.1535342713149775</v>
       </c>
       <c r="C11">
-        <v>77.57922694728265</v>
+        <v>76.79386694895982</v>
       </c>
       <c r="D11">
-        <v>67.46622694728265</v>
+        <v>67.52386694895981</v>
       </c>
       <c r="E11">
-        <v>-19.613</v>
+        <v>-18.77</v>
       </c>
       <c r="F11">
-        <v>7.587</v>
+        <v>8.43</v>
       </c>
       <c r="G11">
         <v>17.7</v>
@@ -2189,28 +2189,28 @@
         <v>154.1</v>
       </c>
       <c r="M11">
-        <v>0.3816261</v>
+        <v>0.424029</v>
       </c>
       <c r="N11">
-        <v>153.7183739</v>
+        <v>153.675971</v>
       </c>
       <c r="O11">
-        <v>53.80143086499999</v>
+        <v>53.78658985</v>
       </c>
       <c r="P11">
-        <v>99.916943035</v>
+        <v>99.88938115000001</v>
       </c>
       <c r="Q11">
-        <v>114.516943035</v>
+        <v>114.48938115</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1660640335006044</v>
+        <v>0.1669608570166417</v>
       </c>
       <c r="T11">
-        <v>0.7355198578549942</v>
+        <v>0.7410047188382528</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>403.7983775218729</v>
+        <v>363.4185397696856</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1535342713149775</v>
+        <v>0.1530077221444051</v>
       </c>
       <c r="C12">
-        <v>76.79386694895982</v>
+        <v>76.0086055247191</v>
       </c>
       <c r="D12">
-        <v>67.52386694895981</v>
+        <v>67.58160552471909</v>
       </c>
       <c r="E12">
-        <v>-18.77</v>
+        <v>-17.927</v>
       </c>
       <c r="F12">
-        <v>8.43</v>
+        <v>9.273</v>
       </c>
       <c r="G12">
         <v>17.7</v>
@@ -2271,28 +2271,28 @@
         <v>154.1</v>
       </c>
       <c r="M12">
-        <v>0.424029</v>
+        <v>0.4664319</v>
       </c>
       <c r="N12">
-        <v>153.675971</v>
+        <v>153.6335681</v>
       </c>
       <c r="O12">
-        <v>53.78658985</v>
+        <v>53.771748835</v>
       </c>
       <c r="P12">
-        <v>99.88938115000001</v>
+        <v>99.86181926499999</v>
       </c>
       <c r="Q12">
-        <v>114.48938115</v>
+        <v>114.461819265</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1669608570166417</v>
+        <v>0.1678778338701181</v>
       </c>
       <c r="T12">
-        <v>0.7410047188382528</v>
+        <v>0.7466128351245063</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>363.4185397696856</v>
+        <v>330.3804906997142</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1530077221444051</v>
+        <v>0.1524811729738326</v>
       </c>
       <c r="C13">
-        <v>76.0086055247191</v>
+        <v>75.22344292764431</v>
       </c>
       <c r="D13">
-        <v>67.58160552471909</v>
+        <v>67.63944292764431</v>
       </c>
       <c r="E13">
-        <v>-17.927</v>
+        <v>-17.084</v>
       </c>
       <c r="F13">
-        <v>9.273</v>
+        <v>10.116</v>
       </c>
       <c r="G13">
         <v>17.7</v>
@@ -2353,28 +2353,28 @@
         <v>154.1</v>
       </c>
       <c r="M13">
-        <v>0.4664319</v>
+        <v>0.5088347999999999</v>
       </c>
       <c r="N13">
-        <v>153.6335681</v>
+        <v>153.5911652</v>
       </c>
       <c r="O13">
-        <v>53.771748835</v>
+        <v>53.75690782</v>
       </c>
       <c r="P13">
-        <v>99.86181926499999</v>
+        <v>99.83425738</v>
       </c>
       <c r="Q13">
-        <v>114.461819265</v>
+        <v>114.43425738</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1678778338701181</v>
+        <v>0.168815651106628</v>
       </c>
       <c r="T13">
-        <v>0.7466128351245063</v>
+        <v>0.7523484085990834</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>330.3804906997142</v>
+        <v>302.8487831414047</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1524811729738326</v>
+        <v>0.1519546238032602</v>
       </c>
       <c r="C14">
-        <v>75.22344292764431</v>
+        <v>74.43837941168628</v>
       </c>
       <c r="D14">
-        <v>67.63944292764431</v>
+        <v>67.69737941168628</v>
       </c>
       <c r="E14">
-        <v>-17.084</v>
+        <v>-16.241</v>
       </c>
       <c r="F14">
-        <v>10.116</v>
+        <v>10.959</v>
       </c>
       <c r="G14">
         <v>17.7</v>
@@ -2435,28 +2435,28 @@
         <v>154.1</v>
       </c>
       <c r="M14">
-        <v>0.5088347999999999</v>
+        <v>0.5512376999999999</v>
       </c>
       <c r="N14">
-        <v>153.5911652</v>
+        <v>153.5487623</v>
       </c>
       <c r="O14">
-        <v>53.75690782</v>
+        <v>53.74206680499999</v>
       </c>
       <c r="P14">
-        <v>99.83425738</v>
+        <v>99.806695495</v>
       </c>
       <c r="Q14">
-        <v>114.43425738</v>
+        <v>114.406695495</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.168815651106628</v>
+        <v>0.1697750273600692</v>
       </c>
       <c r="T14">
-        <v>0.7523484085990834</v>
+        <v>0.758215834337444</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>302.8487831414047</v>
+        <v>279.5527228997581</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1519546238032602</v>
+        <v>0.1514280746326877</v>
       </c>
       <c r="C15">
-        <v>74.43837941168628</v>
+        <v>73.65341523166673</v>
       </c>
       <c r="D15">
-        <v>67.69737941168628</v>
+        <v>67.75541523166673</v>
       </c>
       <c r="E15">
-        <v>-16.241</v>
+        <v>-15.398</v>
       </c>
       <c r="F15">
-        <v>10.959</v>
+        <v>11.802</v>
       </c>
       <c r="G15">
         <v>17.7</v>
@@ -2517,28 +2517,28 @@
         <v>154.1</v>
       </c>
       <c r="M15">
-        <v>0.5512376999999999</v>
+        <v>0.5936406000000001</v>
       </c>
       <c r="N15">
-        <v>153.5487623</v>
+        <v>153.5063594</v>
       </c>
       <c r="O15">
-        <v>53.74206680499999</v>
+        <v>53.72722579</v>
       </c>
       <c r="P15">
-        <v>99.806695495</v>
+        <v>99.77913361</v>
       </c>
       <c r="Q15">
-        <v>114.406695495</v>
+        <v>114.37913361</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1697750273600692</v>
+        <v>0.1707567146891718</v>
       </c>
       <c r="T15">
-        <v>0.758215834337444</v>
+        <v>0.764219711837162</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>279.5527228997581</v>
+        <v>259.5846712640611</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1514280746326877</v>
+        <v>0.1509015254621153</v>
       </c>
       <c r="C16">
-        <v>73.65341523166673</v>
+        <v>72.86855064328194</v>
       </c>
       <c r="D16">
-        <v>67.75541523166673</v>
+        <v>67.81355064328193</v>
       </c>
       <c r="E16">
-        <v>-15.398</v>
+        <v>-14.555</v>
       </c>
       <c r="F16">
-        <v>11.802</v>
+        <v>12.645</v>
       </c>
       <c r="G16">
         <v>17.7</v>
@@ -2599,28 +2599,28 @@
         <v>154.1</v>
       </c>
       <c r="M16">
-        <v>0.5936406000000001</v>
+        <v>0.6360435</v>
       </c>
       <c r="N16">
-        <v>153.5063594</v>
+        <v>153.4639565</v>
       </c>
       <c r="O16">
-        <v>53.72722579</v>
+        <v>53.712384775</v>
       </c>
       <c r="P16">
-        <v>99.77913361</v>
+        <v>99.75157172499999</v>
       </c>
       <c r="Q16">
-        <v>114.37913361</v>
+        <v>114.351571725</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1707567146891718</v>
+        <v>0.171761500543665</v>
       </c>
       <c r="T16">
-        <v>0.764219711837162</v>
+        <v>0.7703648570427555</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>259.5846712640611</v>
+        <v>242.2790265131237</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1509015254621153</v>
+        <v>0.1503749762915428</v>
       </c>
       <c r="C17">
-        <v>72.86855064328194</v>
+        <v>72.08378590310647</v>
       </c>
       <c r="D17">
-        <v>67.81355064328193</v>
+        <v>67.87178590310647</v>
       </c>
       <c r="E17">
-        <v>-14.555</v>
+        <v>-13.712</v>
       </c>
       <c r="F17">
-        <v>12.645</v>
+        <v>13.488</v>
       </c>
       <c r="G17">
         <v>17.7</v>
@@ -2681,28 +2681,28 @@
         <v>154.1</v>
       </c>
       <c r="M17">
-        <v>0.6360435</v>
+        <v>0.6784463999999999</v>
       </c>
       <c r="N17">
-        <v>153.4639565</v>
+        <v>153.4215536</v>
       </c>
       <c r="O17">
-        <v>53.712384775</v>
+        <v>53.69754375999999</v>
       </c>
       <c r="P17">
-        <v>99.75157172499999</v>
+        <v>99.72400983999999</v>
       </c>
       <c r="Q17">
-        <v>114.351571725</v>
+        <v>114.32400984</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.171761500543665</v>
+        <v>0.1727902098708843</v>
       </c>
       <c r="T17">
-        <v>0.7703648570427555</v>
+        <v>0.7766563152294346</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>242.2790265131237</v>
+        <v>227.1365873560535</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1503749762915428</v>
+        <v>0.1498484271209704</v>
       </c>
       <c r="C18">
-        <v>72.08378590310647</v>
+        <v>71.29912126859705</v>
       </c>
       <c r="D18">
-        <v>67.87178590310647</v>
+        <v>67.93012126859705</v>
       </c>
       <c r="E18">
-        <v>-13.712</v>
+        <v>-12.869</v>
       </c>
       <c r="F18">
-        <v>13.488</v>
+        <v>14.331</v>
       </c>
       <c r="G18">
         <v>17.7</v>
@@ -2763,28 +2763,28 @@
         <v>154.1</v>
       </c>
       <c r="M18">
-        <v>0.6784463999999999</v>
+        <v>0.7208493</v>
       </c>
       <c r="N18">
-        <v>153.4215536</v>
+        <v>153.3791507</v>
       </c>
       <c r="O18">
-        <v>53.69754375999999</v>
+        <v>53.68270274499999</v>
       </c>
       <c r="P18">
-        <v>99.72400983999999</v>
+        <v>99.696447955</v>
       </c>
       <c r="Q18">
-        <v>114.32400984</v>
+        <v>114.296447955</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1727902098708843</v>
+        <v>0.1738437073746631</v>
       </c>
       <c r="T18">
-        <v>0.7766563152294346</v>
+        <v>0.7830993748182024</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>227.1365873560535</v>
+        <v>213.7756116292268</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1498484271209704</v>
+        <v>0.1493218779503979</v>
       </c>
       <c r="C19">
-        <v>71.29912126859705</v>
+        <v>70.51455699809623</v>
       </c>
       <c r="D19">
-        <v>67.93012126859705</v>
+        <v>67.98855699809623</v>
       </c>
       <c r="E19">
-        <v>-12.869</v>
+        <v>-12.026</v>
       </c>
       <c r="F19">
-        <v>14.331</v>
+        <v>15.174</v>
       </c>
       <c r="G19">
         <v>17.7</v>
@@ -2845,28 +2845,28 @@
         <v>154.1</v>
       </c>
       <c r="M19">
-        <v>0.7208493</v>
+        <v>0.7632522</v>
       </c>
       <c r="N19">
-        <v>153.3791507</v>
+        <v>153.3367478</v>
       </c>
       <c r="O19">
-        <v>53.68270274499999</v>
+        <v>53.66786172999999</v>
       </c>
       <c r="P19">
-        <v>99.696447955</v>
+        <v>99.66888606999999</v>
       </c>
       <c r="Q19">
-        <v>114.296447955</v>
+        <v>114.26888607</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1738437073746631</v>
+        <v>0.1749228999395096</v>
       </c>
       <c r="T19">
-        <v>0.7830993748182024</v>
+        <v>0.789699582201818</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>213.7756116292268</v>
+        <v>201.8991887609364</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1493218779503979</v>
+        <v>0.1487953287798255</v>
       </c>
       <c r="C20">
-        <v>70.51455699809623</v>
+        <v>69.73009335083633</v>
       </c>
       <c r="D20">
-        <v>67.98855699809623</v>
+        <v>68.04709335083632</v>
       </c>
       <c r="E20">
-        <v>-12.026</v>
+        <v>-11.183</v>
       </c>
       <c r="F20">
-        <v>15.174</v>
+        <v>16.017</v>
       </c>
       <c r="G20">
         <v>17.7</v>
@@ -2927,28 +2927,28 @@
         <v>154.1</v>
       </c>
       <c r="M20">
-        <v>0.7632521999999999</v>
+        <v>0.8056551</v>
       </c>
       <c r="N20">
-        <v>153.3367478</v>
+        <v>153.2943449</v>
       </c>
       <c r="O20">
-        <v>53.66786172999999</v>
+        <v>53.653020715</v>
       </c>
       <c r="P20">
-        <v>99.66888606999999</v>
+        <v>99.641324185</v>
       </c>
       <c r="Q20">
-        <v>114.26888607</v>
+        <v>114.241324185</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1749228999395096</v>
+        <v>0.1760287392343524</v>
       </c>
       <c r="T20">
-        <v>0.789699582201818</v>
+        <v>0.79646275766898</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>201.8991887609364</v>
+        <v>191.2729156682556</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1487953287798255</v>
+        <v>0.148268779609253</v>
       </c>
       <c r="C21">
-        <v>69.73009335083633</v>
+        <v>68.94573058694314</v>
       </c>
       <c r="D21">
-        <v>68.04709335083632</v>
+        <v>68.10573058694314</v>
       </c>
       <c r="E21">
-        <v>-11.183</v>
+        <v>-10.34</v>
       </c>
       <c r="F21">
-        <v>16.017</v>
+        <v>16.86</v>
       </c>
       <c r="G21">
         <v>17.7</v>
@@ -3009,28 +3009,28 @@
         <v>154.1</v>
       </c>
       <c r="M21">
-        <v>0.8056551</v>
+        <v>0.848058</v>
       </c>
       <c r="N21">
-        <v>153.2943449</v>
+        <v>153.251942</v>
       </c>
       <c r="O21">
-        <v>53.653020715</v>
+        <v>53.63817969999999</v>
       </c>
       <c r="P21">
-        <v>99.641324185</v>
+        <v>99.61376229999999</v>
       </c>
       <c r="Q21">
-        <v>114.241324185</v>
+        <v>114.2137623</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1760287392343524</v>
+        <v>0.1771622245115662</v>
       </c>
       <c r="T21">
-        <v>0.79646275766898</v>
+        <v>0.8033950125228209</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>191.2729156682556</v>
+        <v>181.7092698848428</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.148268779609253</v>
+        <v>0.1477422304386805</v>
       </c>
       <c r="C22">
-        <v>68.94573058694314</v>
+        <v>68.16146896743987</v>
       </c>
       <c r="D22">
-        <v>68.10573058694314</v>
+        <v>68.16446896743987</v>
       </c>
       <c r="E22">
-        <v>-10.34</v>
+        <v>-9.497</v>
       </c>
       <c r="F22">
-        <v>16.86</v>
+        <v>17.703</v>
       </c>
       <c r="G22">
         <v>17.7</v>
@@ -3091,28 +3091,28 @@
         <v>154.1</v>
       </c>
       <c r="M22">
-        <v>0.848058</v>
+        <v>0.8904608999999999</v>
       </c>
       <c r="N22">
-        <v>153.251942</v>
+        <v>153.2095391</v>
       </c>
       <c r="O22">
-        <v>53.63817969999999</v>
+        <v>53.623338685</v>
       </c>
       <c r="P22">
-        <v>99.61376229999999</v>
+        <v>99.58620041500001</v>
       </c>
       <c r="Q22">
-        <v>114.2137623</v>
+        <v>114.186200415</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1771622245115662</v>
+        <v>0.178324405618583</v>
       </c>
       <c r="T22">
-        <v>0.8033950125228209</v>
+        <v>0.8105027674995438</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>181.7092698848428</v>
+        <v>173.0564475093741</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1477422304386805</v>
+        <v>0.1472156812681081</v>
       </c>
       <c r="C23">
-        <v>68.16146896743987</v>
+        <v>67.37730875425106</v>
       </c>
       <c r="D23">
-        <v>68.16446896743987</v>
+        <v>68.22330875425105</v>
       </c>
       <c r="E23">
-        <v>-9.497</v>
+        <v>-8.654</v>
       </c>
       <c r="F23">
-        <v>17.703</v>
+        <v>18.546</v>
       </c>
       <c r="G23">
         <v>17.7</v>
@@ -3173,28 +3173,28 @@
         <v>154.1</v>
       </c>
       <c r="M23">
-        <v>0.8904608999999999</v>
+        <v>0.9328637999999999</v>
       </c>
       <c r="N23">
-        <v>153.2095391</v>
+        <v>153.1671362</v>
       </c>
       <c r="O23">
-        <v>53.623338685</v>
+        <v>53.60849766999999</v>
       </c>
       <c r="P23">
-        <v>99.58620041500001</v>
+        <v>99.55863853</v>
       </c>
       <c r="Q23">
-        <v>114.186200415</v>
+        <v>114.15863853</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.178324405618583</v>
+        <v>0.1795163862411642</v>
       </c>
       <c r="T23">
-        <v>0.8105027674995438</v>
+        <v>0.817792772603875</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>173.0564475093741</v>
+        <v>165.1902453498571</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1472156812681081</v>
+        <v>0.1466891320975356</v>
       </c>
       <c r="C24">
-        <v>67.37730875425106</v>
+        <v>66.59325021020626</v>
       </c>
       <c r="D24">
-        <v>68.22330875425105</v>
+        <v>68.28225021020626</v>
       </c>
       <c r="E24">
-        <v>-8.654</v>
+        <v>-7.811</v>
       </c>
       <c r="F24">
-        <v>18.546</v>
+        <v>19.389</v>
       </c>
       <c r="G24">
         <v>17.7</v>
@@ -3255,28 +3255,28 @@
         <v>154.1</v>
       </c>
       <c r="M24">
-        <v>0.9328637999999999</v>
+        <v>0.9752666999999999</v>
       </c>
       <c r="N24">
-        <v>153.1671362</v>
+        <v>153.1247333</v>
       </c>
       <c r="O24">
-        <v>53.60849766999999</v>
+        <v>53.593656655</v>
       </c>
       <c r="P24">
-        <v>99.55863853</v>
+        <v>99.53107664500001</v>
       </c>
       <c r="Q24">
-        <v>114.15863853</v>
+        <v>114.131076645</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1795163862411642</v>
+        <v>0.1807393273993969</v>
       </c>
       <c r="T24">
-        <v>0.817792772603875</v>
+        <v>0.8252721284901369</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>165.1902453498571</v>
+        <v>158.0080607694285</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1466891320975356</v>
+        <v>0.1461625829269632</v>
       </c>
       <c r="C25">
-        <v>66.59325021020626</v>
+        <v>65.80929359904424</v>
       </c>
       <c r="D25">
-        <v>68.28225021020626</v>
+        <v>68.34129359904423</v>
       </c>
       <c r="E25">
-        <v>-7.811</v>
+        <v>-6.968</v>
       </c>
       <c r="F25">
-        <v>19.389</v>
+        <v>20.232</v>
       </c>
       <c r="G25">
         <v>17.7</v>
@@ -3337,28 +3337,28 @@
         <v>154.1</v>
       </c>
       <c r="M25">
-        <v>0.9752666999999999</v>
+        <v>1.0176696</v>
       </c>
       <c r="N25">
-        <v>153.1247333</v>
+        <v>153.0823304</v>
       </c>
       <c r="O25">
-        <v>53.593656655</v>
+        <v>53.57881563999999</v>
       </c>
       <c r="P25">
-        <v>99.53107664500001</v>
+        <v>99.50351476</v>
       </c>
       <c r="Q25">
-        <v>114.131076645</v>
+        <v>114.10351476</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1807393273993969</v>
+        <v>0.1819944512196884</v>
       </c>
       <c r="T25">
-        <v>0.8252721284901369</v>
+        <v>0.8329483095313003</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>158.0080607694285</v>
+        <v>151.4243915707023</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1461625829269632</v>
+        <v>0.1456360337563907</v>
       </c>
       <c r="C26">
-        <v>65.80929359904424</v>
+        <v>65.02543918541669</v>
       </c>
       <c r="D26">
-        <v>68.34129359904423</v>
+        <v>68.40043918541669</v>
       </c>
       <c r="E26">
-        <v>-6.968</v>
+        <v>-6.125</v>
       </c>
       <c r="F26">
-        <v>20.232</v>
+        <v>21.075</v>
       </c>
       <c r="G26">
         <v>17.7</v>
@@ -3419,28 +3419,28 @@
         <v>154.1</v>
       </c>
       <c r="M26">
-        <v>1.0176696</v>
+        <v>1.0600725</v>
       </c>
       <c r="N26">
-        <v>153.0823304</v>
+        <v>153.0399275</v>
       </c>
       <c r="O26">
-        <v>53.57881563999999</v>
+        <v>53.563974625</v>
       </c>
       <c r="P26">
-        <v>99.50351476</v>
+        <v>99.475952875</v>
       </c>
       <c r="Q26">
-        <v>114.10351476</v>
+        <v>114.075952875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1819944512196884</v>
+        <v>0.1832830450085209</v>
       </c>
       <c r="T26">
-        <v>0.8329483095313003</v>
+        <v>0.8408291887335616</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>151.4243915707023</v>
+        <v>145.3674159078742</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1456360337563907</v>
+        <v>0.1451094845858182</v>
       </c>
       <c r="C27">
-        <v>65.02543918541669</v>
+        <v>64.24168723489228</v>
       </c>
       <c r="D27">
-        <v>68.40043918541669</v>
+        <v>68.45968723489227</v>
       </c>
       <c r="E27">
-        <v>-6.125</v>
+        <v>-5.282</v>
       </c>
       <c r="F27">
-        <v>21.075</v>
+        <v>21.918</v>
       </c>
       <c r="G27">
         <v>17.7</v>
@@ -3501,28 +3501,28 @@
         <v>154.1</v>
       </c>
       <c r="M27">
-        <v>1.0600725</v>
+        <v>1.1024754</v>
       </c>
       <c r="N27">
-        <v>153.0399275</v>
+        <v>152.9975246</v>
       </c>
       <c r="O27">
-        <v>53.563974625</v>
+        <v>53.54913360999999</v>
       </c>
       <c r="P27">
-        <v>99.475952875</v>
+        <v>99.44839099000001</v>
       </c>
       <c r="Q27">
-        <v>114.075952875</v>
+        <v>114.04839099</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1832830450085209</v>
+        <v>0.1846064656565111</v>
       </c>
       <c r="T27">
-        <v>0.8408291887335616</v>
+        <v>0.848923064671019</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>145.3674159078742</v>
+        <v>139.7763614498791</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1451094845858182</v>
+        <v>0.1445829354152458</v>
       </c>
       <c r="C28">
-        <v>64.24168723489228</v>
+        <v>63.45803801396062</v>
       </c>
       <c r="D28">
-        <v>68.45968723489227</v>
+        <v>68.51903801396061</v>
       </c>
       <c r="E28">
-        <v>-5.282</v>
+        <v>-4.439</v>
       </c>
       <c r="F28">
-        <v>21.918</v>
+        <v>22.761</v>
       </c>
       <c r="G28">
         <v>17.7</v>
@@ -3583,28 +3583,28 @@
         <v>154.1</v>
       </c>
       <c r="M28">
-        <v>1.1024754</v>
+        <v>1.1448783</v>
       </c>
       <c r="N28">
-        <v>152.9975246</v>
+        <v>152.9551217</v>
       </c>
       <c r="O28">
-        <v>53.54913360999999</v>
+        <v>53.534292595</v>
       </c>
       <c r="P28">
-        <v>99.44839099000001</v>
+        <v>99.42082910500001</v>
       </c>
       <c r="Q28">
-        <v>114.04839099</v>
+        <v>114.020829105</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1846064656565111</v>
+        <v>0.1859661444044463</v>
       </c>
       <c r="T28">
-        <v>0.848923064671019</v>
+        <v>0.8572386906341602</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>139.7763614498791</v>
+        <v>134.5994591739577</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1445829354152458</v>
+        <v>0.1440563862446733</v>
       </c>
       <c r="C29">
-        <v>63.45803801396062</v>
+        <v>62.67449179003623</v>
       </c>
       <c r="D29">
-        <v>68.51903801396061</v>
+        <v>68.57849179003622</v>
       </c>
       <c r="E29">
-        <v>-4.439</v>
+        <v>-3.595999999999997</v>
       </c>
       <c r="F29">
-        <v>22.761</v>
+        <v>23.604</v>
       </c>
       <c r="G29">
         <v>17.7</v>
@@ -3665,28 +3665,28 @@
         <v>154.1</v>
       </c>
       <c r="M29">
-        <v>1.1448783</v>
+        <v>1.1872812</v>
       </c>
       <c r="N29">
-        <v>152.9551217</v>
+        <v>152.9127188</v>
       </c>
       <c r="O29">
-        <v>53.534292595</v>
+        <v>53.51945157999999</v>
       </c>
       <c r="P29">
-        <v>99.42082910500001</v>
+        <v>99.39326722</v>
       </c>
       <c r="Q29">
-        <v>114.020829105</v>
+        <v>113.99326722</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1859661444044463</v>
+        <v>0.1873635920064907</v>
       </c>
       <c r="T29">
-        <v>0.8572386906341602</v>
+        <v>0.8657853062073887</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>134.5994591739577</v>
+        <v>129.7923356320305</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1440563862446733</v>
+        <v>0.1435298370741009</v>
       </c>
       <c r="C30">
-        <v>62.67449179003623</v>
+        <v>61.89104883146261</v>
       </c>
       <c r="D30">
-        <v>68.57849179003622</v>
+        <v>68.63804883146261</v>
       </c>
       <c r="E30">
-        <v>-3.595999999999997</v>
+        <v>-2.752999999999997</v>
       </c>
       <c r="F30">
-        <v>23.604</v>
+        <v>24.447</v>
       </c>
       <c r="G30">
         <v>17.7</v>
@@ -3747,28 +3747,28 @@
         <v>154.1</v>
       </c>
       <c r="M30">
-        <v>1.1872812</v>
+        <v>1.2296841</v>
       </c>
       <c r="N30">
-        <v>152.9127188</v>
+        <v>152.8703159</v>
       </c>
       <c r="O30">
-        <v>53.51945157999999</v>
+        <v>53.50461056499999</v>
       </c>
       <c r="P30">
-        <v>99.39326722</v>
+        <v>99.36570533499999</v>
       </c>
       <c r="Q30">
-        <v>113.99326722</v>
+        <v>113.965705335</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1873635920064907</v>
+        <v>0.1888004043297195</v>
       </c>
       <c r="T30">
-        <v>0.8657853062073887</v>
+        <v>0.8745726715150743</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>129.7923356320305</v>
+        <v>125.3167378516157</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1435298370741009</v>
+        <v>0.1430032879035284</v>
       </c>
       <c r="C31">
-        <v>61.89104883146261</v>
+        <v>61.10770940751622</v>
       </c>
       <c r="D31">
-        <v>68.63804883146261</v>
+        <v>68.69770940751621</v>
       </c>
       <c r="E31">
-        <v>-2.753</v>
+        <v>-1.91</v>
       </c>
       <c r="F31">
-        <v>24.447</v>
+        <v>25.29</v>
       </c>
       <c r="G31">
         <v>17.7</v>
@@ -3829,28 +3829,28 @@
         <v>154.1</v>
       </c>
       <c r="M31">
-        <v>1.2296841</v>
+        <v>1.272087</v>
       </c>
       <c r="N31">
-        <v>152.8703159</v>
+        <v>152.827913</v>
       </c>
       <c r="O31">
-        <v>53.504610565</v>
+        <v>53.48976955</v>
       </c>
       <c r="P31">
-        <v>99.365705335</v>
+        <v>99.33814344999999</v>
       </c>
       <c r="Q31">
-        <v>113.965705335</v>
+        <v>113.93814345</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1888004043297195</v>
+        <v>0.190278268433612</v>
       </c>
       <c r="T31">
-        <v>0.8745726715150743</v>
+        <v>0.8836111044029795</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>125.3167378516157</v>
+        <v>121.1395132565619</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1430032879035284</v>
+        <v>0.1424767387329559</v>
       </c>
       <c r="C32">
-        <v>61.10770940751622</v>
+        <v>60.32447378841056</v>
       </c>
       <c r="D32">
-        <v>68.69770940751621</v>
+        <v>68.75747378841055</v>
       </c>
       <c r="E32">
-        <v>-1.91</v>
+        <v>-1.067</v>
       </c>
       <c r="F32">
-        <v>25.29</v>
+        <v>26.133</v>
       </c>
       <c r="G32">
         <v>17.7</v>
@@ -3911,28 +3911,28 @@
         <v>154.1</v>
       </c>
       <c r="M32">
-        <v>1.272087</v>
+        <v>1.3144899</v>
       </c>
       <c r="N32">
-        <v>152.827913</v>
+        <v>152.7855101</v>
       </c>
       <c r="O32">
-        <v>53.48976955</v>
+        <v>53.47492853499999</v>
       </c>
       <c r="P32">
-        <v>99.33814344999999</v>
+        <v>99.31058156499999</v>
       </c>
       <c r="Q32">
-        <v>113.93814345</v>
+        <v>113.910581565</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.190278268433612</v>
+        <v>0.191798969178197</v>
       </c>
       <c r="T32">
-        <v>0.8836111044029795</v>
+        <v>0.8929115208528531</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>121.1395132565619</v>
+        <v>117.2317870224792</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1424767387329559</v>
+        <v>0.1419501895623835</v>
       </c>
       <c r="C33">
-        <v>60.32447378841056</v>
+        <v>59.54134224530023</v>
       </c>
       <c r="D33">
-        <v>68.75747378841055</v>
+        <v>68.81734224530022</v>
       </c>
       <c r="E33">
-        <v>-1.067</v>
+        <v>-0.2240000000000002</v>
       </c>
       <c r="F33">
-        <v>26.133</v>
+        <v>26.976</v>
       </c>
       <c r="G33">
         <v>17.7</v>
@@ -3993,28 +3993,28 @@
         <v>154.1</v>
       </c>
       <c r="M33">
-        <v>1.3144899</v>
+        <v>1.3568928</v>
       </c>
       <c r="N33">
-        <v>152.7855101</v>
+        <v>152.7431072</v>
       </c>
       <c r="O33">
-        <v>53.47492853499999</v>
+        <v>53.46008751999999</v>
       </c>
       <c r="P33">
-        <v>99.31058156499999</v>
+        <v>99.28301968</v>
       </c>
       <c r="Q33">
-        <v>113.910581565</v>
+        <v>113.88301968</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.191798969178197</v>
+        <v>0.1933643964152698</v>
       </c>
       <c r="T33">
-        <v>0.8929115208528531</v>
+        <v>0.9024854789630169</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>117.2317870224792</v>
+        <v>113.5682936780267</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1419501895623835</v>
+        <v>0.141423640391811</v>
       </c>
       <c r="C34">
-        <v>59.54134224530023</v>
+        <v>58.75831505028509</v>
       </c>
       <c r="D34">
-        <v>68.81734224530022</v>
+        <v>68.87731505028509</v>
       </c>
       <c r="E34">
-        <v>-0.2240000000000002</v>
+        <v>0.6189999999999998</v>
       </c>
       <c r="F34">
-        <v>26.976</v>
+        <v>27.819</v>
       </c>
       <c r="G34">
         <v>17.7</v>
@@ -4075,28 +4075,28 @@
         <v>154.1</v>
       </c>
       <c r="M34">
-        <v>1.3568928</v>
+        <v>1.3992957</v>
       </c>
       <c r="N34">
-        <v>152.7431072</v>
+        <v>152.7007043</v>
       </c>
       <c r="O34">
-        <v>53.46008751999999</v>
+        <v>53.44524650499999</v>
       </c>
       <c r="P34">
-        <v>99.28301968</v>
+        <v>99.25545779499998</v>
       </c>
       <c r="Q34">
-        <v>113.88301968</v>
+        <v>113.855457795</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1933643964152698</v>
+        <v>0.1949765528235986</v>
       </c>
       <c r="T34">
-        <v>0.9024854789630169</v>
+        <v>0.9123452268675141</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>113.5682936780267</v>
+        <v>110.126830233238</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.141423640391811</v>
+        <v>0.1408970912212386</v>
       </c>
       <c r="C35">
-        <v>58.75831505028509</v>
+        <v>57.97539247641434</v>
       </c>
       <c r="D35">
-        <v>68.87731505028509</v>
+        <v>68.93739247641435</v>
       </c>
       <c r="E35">
-        <v>0.6189999999999998</v>
+        <v>1.462000000000003</v>
       </c>
       <c r="F35">
-        <v>27.819</v>
+        <v>28.662</v>
       </c>
       <c r="G35">
         <v>17.7</v>
@@ -4157,28 +4157,28 @@
         <v>154.1</v>
       </c>
       <c r="M35">
-        <v>1.3992957</v>
+        <v>1.4416986</v>
       </c>
       <c r="N35">
-        <v>152.7007043</v>
+        <v>152.6583014</v>
       </c>
       <c r="O35">
-        <v>53.44524650499999</v>
+        <v>53.43040549</v>
       </c>
       <c r="P35">
-        <v>99.25545779499998</v>
+        <v>99.22789591</v>
       </c>
       <c r="Q35">
-        <v>113.855457795</v>
+        <v>113.82789591</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1949765528235986</v>
+        <v>0.1966375624564221</v>
       </c>
       <c r="T35">
-        <v>0.9123452268675141</v>
+        <v>0.9225037550115415</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>110.126830233238</v>
+        <v>106.8878058146134</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1408970912212386</v>
+        <v>0.1403705420506661</v>
       </c>
       <c r="C36">
-        <v>57.97539247641434</v>
+        <v>57.19257479769067</v>
       </c>
       <c r="D36">
-        <v>68.93739247641435</v>
+        <v>68.99757479769067</v>
       </c>
       <c r="E36">
-        <v>1.462000000000003</v>
+        <v>2.305000000000003</v>
       </c>
       <c r="F36">
-        <v>28.662</v>
+        <v>29.505</v>
       </c>
       <c r="G36">
         <v>17.7</v>
@@ -4239,28 +4239,28 @@
         <v>154.1</v>
       </c>
       <c r="M36">
-        <v>1.4416986</v>
+        <v>1.4841015</v>
       </c>
       <c r="N36">
-        <v>152.6583014</v>
+        <v>152.6158985</v>
       </c>
       <c r="O36">
-        <v>53.43040549</v>
+        <v>53.41556447499999</v>
       </c>
       <c r="P36">
-        <v>99.22789591</v>
+        <v>99.20033402499999</v>
       </c>
       <c r="Q36">
-        <v>113.82789591</v>
+        <v>113.800334025</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1966375624564221</v>
+        <v>0.1983496800779479</v>
       </c>
       <c r="T36">
-        <v>0.9225037550115415</v>
+        <v>0.9329748532523081</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>106.8878058146134</v>
+        <v>103.8338685056244</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1403705420506661</v>
+        <v>0.1398439928800937</v>
       </c>
       <c r="C37">
-        <v>57.19257479769067</v>
+        <v>56.40986228907437</v>
       </c>
       <c r="D37">
-        <v>68.99757479769067</v>
+        <v>69.05786228907436</v>
       </c>
       <c r="E37">
-        <v>2.305000000000003</v>
+        <v>3.148000000000003</v>
       </c>
       <c r="F37">
-        <v>29.505</v>
+        <v>30.348</v>
       </c>
       <c r="G37">
         <v>17.7</v>
@@ -4321,28 +4321,28 @@
         <v>154.1</v>
       </c>
       <c r="M37">
-        <v>1.4841015</v>
+        <v>1.5265044</v>
       </c>
       <c r="N37">
-        <v>152.6158985</v>
+        <v>152.5734956</v>
       </c>
       <c r="O37">
-        <v>53.41556447499999</v>
+        <v>53.40072345999999</v>
       </c>
       <c r="P37">
-        <v>99.20033402499999</v>
+        <v>99.17277214000001</v>
       </c>
       <c r="Q37">
-        <v>113.800334025</v>
+        <v>113.77277214</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1983496800779479</v>
+        <v>0.2001153013751464</v>
       </c>
       <c r="T37">
-        <v>0.9329748532523081</v>
+        <v>0.9437731733130986</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>103.8338685056244</v>
+        <v>100.9495943804682</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1398439928800937</v>
+        <v>0.1393174437095212</v>
       </c>
       <c r="C38">
-        <v>56.40986228907437</v>
+        <v>55.62725522648762</v>
       </c>
       <c r="D38">
-        <v>69.05786228907436</v>
+        <v>69.11825522648762</v>
       </c>
       <c r="E38">
-        <v>3.148</v>
+        <v>3.991</v>
       </c>
       <c r="F38">
-        <v>30.348</v>
+        <v>31.191</v>
       </c>
       <c r="G38">
         <v>17.7</v>
@@ -4403,28 +4403,28 @@
         <v>154.1</v>
       </c>
       <c r="M38">
-        <v>1.5265044</v>
+        <v>1.5689073</v>
       </c>
       <c r="N38">
-        <v>152.5734956</v>
+        <v>152.5310927</v>
       </c>
       <c r="O38">
-        <v>53.40072345999999</v>
+        <v>53.38588244499999</v>
       </c>
       <c r="P38">
-        <v>99.17277214000001</v>
+        <v>99.14521025499999</v>
       </c>
       <c r="Q38">
-        <v>113.77277214</v>
+        <v>113.745210255</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2001153013751464</v>
+        <v>0.2019369741420971</v>
       </c>
       <c r="T38">
-        <v>0.9437731733130986</v>
+        <v>0.9549142971853428</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>100.9495943804682</v>
+        <v>98.22122696477989</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1393174437095212</v>
+        <v>0.1387908945389487</v>
       </c>
       <c r="C39">
-        <v>55.62725522648762</v>
+        <v>54.84475388681864</v>
       </c>
       <c r="D39">
-        <v>69.11825522648762</v>
+        <v>69.17875388681864</v>
       </c>
       <c r="E39">
-        <v>3.991</v>
+        <v>4.834</v>
       </c>
       <c r="F39">
-        <v>31.191</v>
+        <v>32.034</v>
       </c>
       <c r="G39">
         <v>17.7</v>
@@ -4485,28 +4485,28 @@
         <v>154.1</v>
       </c>
       <c r="M39">
-        <v>1.5689073</v>
+        <v>1.6113102</v>
       </c>
       <c r="N39">
-        <v>152.5310927</v>
+        <v>152.4886898</v>
       </c>
       <c r="O39">
-        <v>53.38588244499999</v>
+        <v>53.37104143</v>
       </c>
       <c r="P39">
-        <v>99.14521025499999</v>
+        <v>99.11764837000001</v>
       </c>
       <c r="Q39">
-        <v>113.745210255</v>
+        <v>113.71764837</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2019369741420971</v>
+        <v>0.2038174105466915</v>
       </c>
       <c r="T39">
-        <v>0.9549142971853428</v>
+        <v>0.9664148121502402</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>98.22122696477989</v>
+        <v>95.63645783412778</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1387908945389487</v>
+        <v>0.1382643453683763</v>
       </c>
       <c r="C40">
-        <v>54.84475388681864</v>
+        <v>54.06235854792595</v>
       </c>
       <c r="D40">
-        <v>69.17875388681864</v>
+        <v>69.23935854792595</v>
       </c>
       <c r="E40">
-        <v>4.834</v>
+        <v>5.677000000000003</v>
       </c>
       <c r="F40">
-        <v>32.034</v>
+        <v>32.877</v>
       </c>
       <c r="G40">
         <v>17.7</v>
@@ -4567,28 +4567,28 @@
         <v>154.1</v>
       </c>
       <c r="M40">
-        <v>1.6113102</v>
+        <v>1.6537131</v>
       </c>
       <c r="N40">
-        <v>152.4886898</v>
+        <v>152.4462869</v>
       </c>
       <c r="O40">
-        <v>53.37104143</v>
+        <v>53.356200415</v>
       </c>
       <c r="P40">
-        <v>99.11764837000001</v>
+        <v>99.090086485</v>
       </c>
       <c r="Q40">
-        <v>113.71764837</v>
+        <v>113.690086485</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2038174105466915</v>
+        <v>0.2057595006038956</v>
       </c>
       <c r="T40">
-        <v>0.9664148121502402</v>
+        <v>0.9782923931795605</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>95.63645783412778</v>
+        <v>93.18424096658603</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1382643453683763</v>
+        <v>0.1377377961978038</v>
       </c>
       <c r="C41">
-        <v>54.06235854792595</v>
+        <v>53.28006948864255</v>
       </c>
       <c r="D41">
-        <v>69.23935854792595</v>
+        <v>69.30006948864255</v>
       </c>
       <c r="E41">
-        <v>5.677000000000003</v>
+        <v>6.52</v>
       </c>
       <c r="F41">
-        <v>32.877</v>
+        <v>33.72</v>
       </c>
       <c r="G41">
         <v>17.7</v>
@@ -4649,28 +4649,28 @@
         <v>154.1</v>
       </c>
       <c r="M41">
-        <v>1.6537131</v>
+        <v>1.696116</v>
       </c>
       <c r="N41">
-        <v>152.4462869</v>
+        <v>152.403884</v>
       </c>
       <c r="O41">
-        <v>53.356200415</v>
+        <v>53.3413594</v>
       </c>
       <c r="P41">
-        <v>99.090086485</v>
+        <v>99.0625246</v>
       </c>
       <c r="Q41">
-        <v>113.690086485</v>
+        <v>113.6625246</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2057595006038956</v>
+        <v>0.2077663269963397</v>
       </c>
       <c r="T41">
-        <v>0.9782923931795605</v>
+        <v>0.9905658935765246</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>93.18424096658603</v>
+        <v>90.8546349424214</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1377377961978038</v>
+        <v>0.1372112470272314</v>
       </c>
       <c r="C42">
-        <v>53.28006948864255</v>
+        <v>52.49788698878032</v>
       </c>
       <c r="D42">
-        <v>69.30006948864255</v>
+        <v>69.36088698878032</v>
       </c>
       <c r="E42">
-        <v>6.52</v>
+        <v>7.363000000000003</v>
       </c>
       <c r="F42">
-        <v>33.72</v>
+        <v>34.563</v>
       </c>
       <c r="G42">
         <v>17.7</v>
@@ -4731,28 +4731,28 @@
         <v>154.1</v>
       </c>
       <c r="M42">
-        <v>1.696116</v>
+        <v>1.7385189</v>
       </c>
       <c r="N42">
-        <v>152.403884</v>
+        <v>152.3614811</v>
       </c>
       <c r="O42">
-        <v>53.3413594</v>
+        <v>53.32651838499999</v>
       </c>
       <c r="P42">
-        <v>99.0625246</v>
+        <v>99.03496271500001</v>
       </c>
       <c r="Q42">
-        <v>113.6625246</v>
+        <v>113.634962715</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2077663269963397</v>
+        <v>0.2098411814020871</v>
       </c>
       <c r="T42">
-        <v>0.9905658935765246</v>
+        <v>1.003255444834403</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>90.8546349424214</v>
+        <v>88.63866823650866</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1372112470272314</v>
+        <v>0.1366846978566589</v>
       </c>
       <c r="C43">
-        <v>52.49788698878032</v>
+        <v>51.71581132913419</v>
       </c>
       <c r="D43">
-        <v>69.36088698878032</v>
+        <v>69.42181132913419</v>
       </c>
       <c r="E43">
-        <v>7.363000000000003</v>
+        <v>8.206</v>
       </c>
       <c r="F43">
-        <v>34.563</v>
+        <v>35.406</v>
       </c>
       <c r="G43">
         <v>17.7</v>
@@ -4813,28 +4813,28 @@
         <v>154.1</v>
       </c>
       <c r="M43">
-        <v>1.7385189</v>
+        <v>1.7809218</v>
       </c>
       <c r="N43">
-        <v>152.3614811</v>
+        <v>152.3190782</v>
       </c>
       <c r="O43">
-        <v>53.32651838499999</v>
+        <v>53.31167737</v>
       </c>
       <c r="P43">
-        <v>99.03496271500001</v>
+        <v>99.00740083000001</v>
       </c>
       <c r="Q43">
-        <v>113.634962715</v>
+        <v>113.60740083</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2098411814020871</v>
+        <v>0.2119875825114809</v>
       </c>
       <c r="T43">
-        <v>1.003255444834403</v>
+        <v>1.016382566825311</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>88.63866823650866</v>
+        <v>86.52822375468705</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1366846978566589</v>
+        <v>0.1361581486860865</v>
       </c>
       <c r="C44">
-        <v>51.71581132913419</v>
+        <v>50.93384279148658</v>
       </c>
       <c r="D44">
-        <v>69.42181132913419</v>
+        <v>69.48284279148658</v>
       </c>
       <c r="E44">
-        <v>8.206</v>
+        <v>9.048999999999996</v>
       </c>
       <c r="F44">
-        <v>35.406</v>
+        <v>36.249</v>
       </c>
       <c r="G44">
         <v>17.7</v>
@@ -4895,28 +4895,28 @@
         <v>154.1</v>
       </c>
       <c r="M44">
-        <v>1.7809218</v>
+        <v>1.8233247</v>
       </c>
       <c r="N44">
-        <v>152.3190782</v>
+        <v>152.2766753</v>
       </c>
       <c r="O44">
-        <v>53.31167737</v>
+        <v>53.296836355</v>
       </c>
       <c r="P44">
-        <v>99.00740083000001</v>
+        <v>98.979838945</v>
       </c>
       <c r="Q44">
-        <v>113.60740083</v>
+        <v>113.579838945</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2119875825114809</v>
+        <v>0.2142092959405026</v>
       </c>
       <c r="T44">
-        <v>1.016382566825311</v>
+        <v>1.029970289587831</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>86.52822375468705</v>
+        <v>84.51593948132223</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1361581486860865</v>
+        <v>0.135631599515514</v>
       </c>
       <c r="C45">
-        <v>50.93384279148658</v>
+        <v>50.15198165861162</v>
       </c>
       <c r="D45">
-        <v>69.48284279148658</v>
+        <v>69.54398165861161</v>
       </c>
       <c r="E45">
-        <v>9.048999999999996</v>
+        <v>9.891999999999999</v>
       </c>
       <c r="F45">
-        <v>36.249</v>
+        <v>37.092</v>
       </c>
       <c r="G45">
         <v>17.7</v>
@@ -4977,28 +4977,28 @@
         <v>154.1</v>
       </c>
       <c r="M45">
-        <v>1.8233247</v>
+        <v>1.8657276</v>
       </c>
       <c r="N45">
-        <v>152.2766753</v>
+        <v>152.2342724</v>
       </c>
       <c r="O45">
-        <v>53.296836355</v>
+        <v>53.28199533999999</v>
       </c>
       <c r="P45">
-        <v>98.979838945</v>
+        <v>98.95227706</v>
       </c>
       <c r="Q45">
-        <v>113.579838945</v>
+        <v>113.55227706</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2142092959405026</v>
+        <v>0.2165103562777036</v>
       </c>
       <c r="T45">
-        <v>1.029970289587831</v>
+        <v>1.044043288163297</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>84.51593948132223</v>
+        <v>82.59512267492853</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.135631599515514</v>
+        <v>0.1351050503449416</v>
       </c>
       <c r="C46">
-        <v>50.15198165861162</v>
+        <v>49.37022821427963</v>
       </c>
       <c r="D46">
-        <v>69.54398165861161</v>
+        <v>69.60522821427963</v>
       </c>
       <c r="E46">
-        <v>9.891999999999999</v>
+        <v>10.735</v>
       </c>
       <c r="F46">
-        <v>37.092</v>
+        <v>37.935</v>
       </c>
       <c r="G46">
         <v>17.7</v>
@@ -5059,28 +5059,28 @@
         <v>154.1</v>
       </c>
       <c r="M46">
-        <v>1.8657276</v>
+        <v>1.9081305</v>
       </c>
       <c r="N46">
-        <v>152.2342724</v>
+        <v>152.1918695</v>
       </c>
       <c r="O46">
-        <v>53.28199533999999</v>
+        <v>53.26715432499999</v>
       </c>
       <c r="P46">
-        <v>98.95227706</v>
+        <v>98.924715175</v>
       </c>
       <c r="Q46">
-        <v>113.55227706</v>
+        <v>113.524715175</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2165103562777036</v>
+        <v>0.2188950915362573</v>
       </c>
       <c r="T46">
-        <v>1.044043288163297</v>
+        <v>1.058628032141508</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>82.59512267492853</v>
+        <v>80.75967550437457</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1351050503449416</v>
+        <v>0.1345785011743691</v>
       </c>
       <c r="C47">
-        <v>49.37022821427963</v>
+        <v>48.5885827432615</v>
       </c>
       <c r="D47">
-        <v>69.60522821427963</v>
+        <v>69.6665827432615</v>
       </c>
       <c r="E47">
-        <v>10.735</v>
+        <v>11.578</v>
       </c>
       <c r="F47">
-        <v>37.935</v>
+        <v>38.778</v>
       </c>
       <c r="G47">
         <v>17.7</v>
@@ -5141,28 +5141,28 @@
         <v>154.1</v>
       </c>
       <c r="M47">
-        <v>1.9081305</v>
+        <v>1.9505334</v>
       </c>
       <c r="N47">
-        <v>152.1918695</v>
+        <v>152.1494666</v>
       </c>
       <c r="O47">
-        <v>53.26715432499999</v>
+        <v>53.25231330999999</v>
       </c>
       <c r="P47">
-        <v>98.924715175</v>
+        <v>98.89715328999999</v>
       </c>
       <c r="Q47">
-        <v>113.524715175</v>
+        <v>113.49715329</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2188950915362573</v>
+        <v>0.2213681503229057</v>
       </c>
       <c r="T47">
-        <v>1.058628032141508</v>
+        <v>1.073752951822615</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>80.75967550437457</v>
+        <v>79.00403038471426</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1345785011743691</v>
+        <v>0.1340519520037966</v>
       </c>
       <c r="C48">
-        <v>48.5885827432615</v>
+        <v>47.80704553133295</v>
       </c>
       <c r="D48">
-        <v>69.6665827432615</v>
+        <v>69.72804553133295</v>
       </c>
       <c r="E48">
-        <v>11.578</v>
+        <v>12.421</v>
       </c>
       <c r="F48">
-        <v>38.778</v>
+        <v>39.621</v>
       </c>
       <c r="G48">
         <v>17.7</v>
@@ -5223,28 +5223,28 @@
         <v>154.1</v>
       </c>
       <c r="M48">
-        <v>1.9505334</v>
+        <v>1.9929363</v>
       </c>
       <c r="N48">
-        <v>152.1494666</v>
+        <v>152.1070637</v>
       </c>
       <c r="O48">
-        <v>53.25231330999999</v>
+        <v>53.237472295</v>
       </c>
       <c r="P48">
-        <v>98.89715328999999</v>
+        <v>98.86959140499999</v>
       </c>
       <c r="Q48">
-        <v>113.49715329</v>
+        <v>113.469591405</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2213681503229057</v>
+        <v>0.2239345320826351</v>
       </c>
       <c r="T48">
-        <v>1.073752951822615</v>
+        <v>1.089448623189802</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>79.00403038471426</v>
+        <v>77.32309356801821</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1340519520037966</v>
+        <v>0.1335254028332242</v>
       </c>
       <c r="C49">
-        <v>47.80704553133295</v>
+        <v>47.0256168652792</v>
       </c>
       <c r="D49">
-        <v>69.72804553133295</v>
+        <v>69.7896168652792</v>
       </c>
       <c r="E49">
-        <v>12.421</v>
+        <v>13.264</v>
       </c>
       <c r="F49">
-        <v>39.621</v>
+        <v>40.464</v>
       </c>
       <c r="G49">
         <v>17.7</v>
@@ -5305,28 +5305,28 @@
         <v>154.1</v>
       </c>
       <c r="M49">
-        <v>1.9929363</v>
+        <v>2.0353392</v>
       </c>
       <c r="N49">
-        <v>152.1070637</v>
+        <v>152.0646608</v>
       </c>
       <c r="O49">
-        <v>53.237472295</v>
+        <v>53.22263127999999</v>
       </c>
       <c r="P49">
-        <v>98.86959140499999</v>
+        <v>98.84202951999998</v>
       </c>
       <c r="Q49">
-        <v>113.469591405</v>
+        <v>113.44202952</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2239345320826351</v>
+        <v>0.2265996208331234</v>
       </c>
       <c r="T49">
-        <v>1.089448623189802</v>
+        <v>1.105747974224958</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>77.32309356801821</v>
+        <v>75.71219578535117</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1335254028332242</v>
+        <v>0.1329988536626517</v>
       </c>
       <c r="C50">
-        <v>47.0256168652792</v>
+        <v>46.24429703289925</v>
       </c>
       <c r="D50">
-        <v>69.7896168652792</v>
+        <v>69.85129703289924</v>
       </c>
       <c r="E50">
-        <v>13.264</v>
+        <v>14.107</v>
       </c>
       <c r="F50">
-        <v>40.464</v>
+        <v>41.307</v>
       </c>
       <c r="G50">
         <v>17.7</v>
@@ -5387,28 +5387,28 @@
         <v>154.1</v>
       </c>
       <c r="M50">
-        <v>2.0353392</v>
+        <v>2.0777421</v>
       </c>
       <c r="N50">
-        <v>152.0646608</v>
+        <v>152.0222579</v>
       </c>
       <c r="O50">
-        <v>53.22263127999999</v>
+        <v>53.207790265</v>
       </c>
       <c r="P50">
-        <v>98.84202951999998</v>
+        <v>98.814467635</v>
       </c>
       <c r="Q50">
-        <v>113.44202952</v>
+        <v>113.414467635</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2265996208331234</v>
+        <v>0.2293692228679445</v>
       </c>
       <c r="T50">
-        <v>1.105747974224958</v>
+        <v>1.122686515496786</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>75.71219578535117</v>
+        <v>74.1670489325889</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1329988536626517</v>
+        <v>0.1324723044920793</v>
       </c>
       <c r="C51">
-        <v>46.24429703289925</v>
+        <v>45.46308632301045</v>
       </c>
       <c r="D51">
-        <v>69.85129703289924</v>
+        <v>69.91308632301045</v>
       </c>
       <c r="E51">
-        <v>14.107</v>
+        <v>14.95</v>
       </c>
       <c r="F51">
-        <v>41.307</v>
+        <v>42.15</v>
       </c>
       <c r="G51">
         <v>17.7</v>
@@ -5469,28 +5469,28 @@
         <v>154.1</v>
       </c>
       <c r="M51">
-        <v>2.0777421</v>
+        <v>2.120145</v>
       </c>
       <c r="N51">
-        <v>152.0222579</v>
+        <v>151.979855</v>
       </c>
       <c r="O51">
-        <v>53.207790265</v>
+        <v>53.19294924999999</v>
       </c>
       <c r="P51">
-        <v>98.814467635</v>
+        <v>98.78690574999999</v>
       </c>
       <c r="Q51">
-        <v>113.414467635</v>
+        <v>113.38690575</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2293692228679445</v>
+        <v>0.2322496089841585</v>
       </c>
       <c r="T51">
-        <v>1.122686515496786</v>
+        <v>1.140302598419487</v>
       </c>
       <c r="U51">
         <v>0.0503</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>74.1670489325889</v>
+        <v>72.6837079539371</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1324723044920793</v>
+        <v>0.1319457553215068</v>
       </c>
       <c r="C52">
-        <v>45.46308632301045</v>
+        <v>44.68198502545297</v>
       </c>
       <c r="D52">
-        <v>69.91308632301045</v>
+        <v>69.97498502545297</v>
       </c>
       <c r="E52">
-        <v>14.95</v>
+        <v>15.793</v>
       </c>
       <c r="F52">
-        <v>42.15</v>
+        <v>42.993</v>
       </c>
       <c r="G52">
         <v>17.7</v>
@@ -5551,28 +5551,28 @@
         <v>154.1</v>
       </c>
       <c r="M52">
-        <v>2.120145</v>
+        <v>2.1625479</v>
       </c>
       <c r="N52">
-        <v>151.979855</v>
+        <v>151.9374521</v>
       </c>
       <c r="O52">
-        <v>53.19294924999999</v>
+        <v>53.178108235</v>
       </c>
       <c r="P52">
-        <v>98.78690574999999</v>
+        <v>98.75934386500001</v>
       </c>
       <c r="Q52">
-        <v>113.38690575</v>
+        <v>113.359343865</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2322496089841585</v>
+        <v>0.2352475618806261</v>
       </c>
       <c r="T52">
-        <v>1.140302598419487</v>
+        <v>1.158637705134952</v>
       </c>
       <c r="U52">
         <v>0.0503</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>72.6837079539371</v>
+        <v>71.25853720974227</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1319457553215068</v>
+        <v>0.1314192061509343</v>
       </c>
       <c r="C53">
-        <v>44.68198502545297</v>
+        <v>43.90099343109439</v>
       </c>
       <c r="D53">
-        <v>69.97498502545297</v>
+        <v>70.03699343109439</v>
       </c>
       <c r="E53">
-        <v>15.793</v>
+        <v>16.636</v>
       </c>
       <c r="F53">
-        <v>42.993</v>
+        <v>43.836</v>
       </c>
       <c r="G53">
         <v>17.7</v>
@@ -5633,28 +5633,28 @@
         <v>154.1</v>
       </c>
       <c r="M53">
-        <v>2.1625479</v>
+        <v>2.2049508</v>
       </c>
       <c r="N53">
-        <v>151.9374521</v>
+        <v>151.8950492</v>
       </c>
       <c r="O53">
-        <v>53.178108235</v>
+        <v>53.16326721999999</v>
       </c>
       <c r="P53">
-        <v>98.75934386500001</v>
+        <v>98.73178197999999</v>
       </c>
       <c r="Q53">
-        <v>113.359343865</v>
+        <v>113.33178198</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2352475618806261</v>
+        <v>0.2383704294811132</v>
       </c>
       <c r="T53">
-        <v>1.158637705134952</v>
+        <v>1.177736774630229</v>
       </c>
       <c r="U53">
         <v>0.0503</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>71.25853720974227</v>
+        <v>69.88818072493953</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1314192061509343</v>
+        <v>0.1308926569803619</v>
       </c>
       <c r="C54">
-        <v>43.90099343109439</v>
+        <v>43.12011183183419</v>
       </c>
       <c r="D54">
-        <v>70.03699343109439</v>
+        <v>70.09911183183419</v>
       </c>
       <c r="E54">
-        <v>16.636</v>
+        <v>17.479</v>
       </c>
       <c r="F54">
-        <v>43.836</v>
+        <v>44.679</v>
       </c>
       <c r="G54">
         <v>17.7</v>
@@ -5715,28 +5715,28 @@
         <v>154.1</v>
       </c>
       <c r="M54">
-        <v>2.2049508</v>
+        <v>2.2473537</v>
       </c>
       <c r="N54">
-        <v>151.8950492</v>
+        <v>151.8526463</v>
       </c>
       <c r="O54">
-        <v>53.16326721999999</v>
+        <v>53.148426205</v>
       </c>
       <c r="P54">
-        <v>98.73178197999999</v>
+        <v>98.70422009500001</v>
       </c>
       <c r="Q54">
-        <v>113.33178198</v>
+        <v>113.304220095</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2383704294811132</v>
+        <v>0.2416261850645998</v>
       </c>
       <c r="T54">
-        <v>1.177736774630229</v>
+        <v>1.197648570487005</v>
       </c>
       <c r="U54">
         <v>0.0503</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>69.88818072493953</v>
+        <v>68.56953580560105</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1308926569803619</v>
+        <v>0.1303661078097894</v>
       </c>
       <c r="C55">
-        <v>43.12011183183419</v>
+        <v>42.33934052060832</v>
       </c>
       <c r="D55">
-        <v>70.09911183183419</v>
+        <v>70.16134052060832</v>
       </c>
       <c r="E55">
-        <v>17.479</v>
+        <v>18.322</v>
       </c>
       <c r="F55">
-        <v>44.679</v>
+        <v>45.522</v>
       </c>
       <c r="G55">
         <v>17.7</v>
@@ -5797,28 +5797,28 @@
         <v>154.1</v>
       </c>
       <c r="M55">
-        <v>2.2473537</v>
+        <v>2.2897566</v>
       </c>
       <c r="N55">
-        <v>151.8526463</v>
+        <v>151.8102434</v>
       </c>
       <c r="O55">
-        <v>53.148426205</v>
+        <v>53.13358518999999</v>
       </c>
       <c r="P55">
-        <v>98.70422009500001</v>
+        <v>98.67665821</v>
       </c>
       <c r="Q55">
-        <v>113.304220095</v>
+        <v>113.27665821</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2416261850645998</v>
+        <v>0.2450234952386727</v>
       </c>
       <c r="T55">
-        <v>1.197648570487005</v>
+        <v>1.218426096598425</v>
       </c>
       <c r="U55">
         <v>0.0503</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>68.56953580560105</v>
+        <v>67.29972958697881</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1303661078097894</v>
+        <v>0.129839558639217</v>
       </c>
       <c r="C56">
-        <v>42.33934052060832</v>
+        <v>41.55867979139391</v>
       </c>
       <c r="D56">
-        <v>70.16134052060832</v>
+        <v>70.22367979139391</v>
       </c>
       <c r="E56">
-        <v>18.322</v>
+        <v>19.165</v>
       </c>
       <c r="F56">
-        <v>45.522</v>
+        <v>46.365</v>
       </c>
       <c r="G56">
         <v>17.7</v>
@@ -5879,28 +5879,28 @@
         <v>154.1</v>
       </c>
       <c r="M56">
-        <v>2.2897566</v>
+        <v>2.3321595</v>
       </c>
       <c r="N56">
-        <v>151.8102434</v>
+        <v>151.7678405</v>
       </c>
       <c r="O56">
-        <v>53.13358518999999</v>
+        <v>53.118744175</v>
       </c>
       <c r="P56">
-        <v>98.67665821</v>
+        <v>98.64909632500002</v>
       </c>
       <c r="Q56">
-        <v>113.27665821</v>
+        <v>113.249096325</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2450234952386727</v>
+        <v>0.2485717969760377</v>
       </c>
       <c r="T56">
-        <v>1.218426096598425</v>
+        <v>1.240127068314796</v>
       </c>
       <c r="U56">
         <v>0.0503</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>67.29972958697881</v>
+        <v>66.07609813994283</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.129839558639217</v>
+        <v>0.1293130094686445</v>
       </c>
       <c r="C57">
-        <v>41.55867979139391</v>
+        <v>40.77812993921376</v>
       </c>
       <c r="D57">
-        <v>70.22367979139391</v>
+        <v>70.28612993921377</v>
       </c>
       <c r="E57">
-        <v>19.165</v>
+        <v>20.00800000000001</v>
       </c>
       <c r="F57">
-        <v>46.365</v>
+        <v>47.20800000000001</v>
       </c>
       <c r="G57">
         <v>17.7</v>
@@ -5961,28 +5961,28 @@
         <v>154.1</v>
       </c>
       <c r="M57">
-        <v>2.3321595</v>
+        <v>2.3745624</v>
       </c>
       <c r="N57">
-        <v>151.7678405</v>
+        <v>151.7254376</v>
       </c>
       <c r="O57">
-        <v>53.118744175</v>
+        <v>53.10390315999999</v>
       </c>
       <c r="P57">
-        <v>98.64909632500002</v>
+        <v>98.62153444</v>
       </c>
       <c r="Q57">
-        <v>113.249096325</v>
+        <v>113.22153444</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2485717969760377</v>
+        <v>0.2522813851560102</v>
       </c>
       <c r="T57">
-        <v>1.240127068314796</v>
+        <v>1.262814447836457</v>
       </c>
       <c r="U57">
         <v>0.0503</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>66.07609813994283</v>
+        <v>64.89616781601526</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1293130094686445</v>
+        <v>0.1287864602980721</v>
       </c>
       <c r="C58">
-        <v>40.77812993921376</v>
+        <v>39.99769126014111</v>
       </c>
       <c r="D58">
-        <v>70.28612993921377</v>
+        <v>70.34869126014111</v>
       </c>
       <c r="E58">
-        <v>20.00800000000001</v>
+        <v>20.851</v>
       </c>
       <c r="F58">
-        <v>47.20800000000001</v>
+        <v>48.051</v>
       </c>
       <c r="G58">
         <v>17.7</v>
@@ -6043,28 +6043,28 @@
         <v>154.1</v>
       </c>
       <c r="M58">
-        <v>2.3745624</v>
+        <v>2.4169653</v>
       </c>
       <c r="N58">
-        <v>151.7254376</v>
+        <v>151.6830347</v>
       </c>
       <c r="O58">
-        <v>53.10390315999999</v>
+        <v>53.089062145</v>
       </c>
       <c r="P58">
-        <v>98.62153444</v>
+        <v>98.59397255500001</v>
       </c>
       <c r="Q58">
-        <v>113.22153444</v>
+        <v>113.193972555</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2522813851560102</v>
+        <v>0.2561635123210978</v>
       </c>
       <c r="T58">
-        <v>1.262814447836457</v>
+        <v>1.286557054312614</v>
       </c>
       <c r="U58">
         <v>0.0503</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>64.89616781601526</v>
+        <v>63.7576385560852</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1287864602980721</v>
+        <v>0.1282599111274996</v>
       </c>
       <c r="C59">
-        <v>39.99769126014111</v>
+        <v>39.21736405130426</v>
       </c>
       <c r="D59">
-        <v>70.34869126014111</v>
+        <v>70.41136405130426</v>
       </c>
       <c r="E59">
-        <v>20.851</v>
+        <v>21.69400000000001</v>
       </c>
       <c r="F59">
-        <v>48.051</v>
+        <v>48.89400000000001</v>
       </c>
       <c r="G59">
         <v>17.7</v>
@@ -6125,28 +6125,28 @@
         <v>154.1</v>
       </c>
       <c r="M59">
-        <v>2.4169653</v>
+        <v>2.4593682</v>
       </c>
       <c r="N59">
-        <v>151.6830347</v>
+        <v>151.6406318</v>
       </c>
       <c r="O59">
-        <v>53.089062145</v>
+        <v>53.07422113</v>
       </c>
       <c r="P59">
-        <v>98.59397255500001</v>
+        <v>98.56641067</v>
       </c>
       <c r="Q59">
-        <v>113.193972555</v>
+        <v>113.16641067</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2561635123210978</v>
+        <v>0.2602305026845229</v>
       </c>
       <c r="T59">
-        <v>1.286557054312614</v>
+        <v>1.31143026109716</v>
       </c>
       <c r="U59">
         <v>0.0503</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>63.7576385560852</v>
+        <v>62.65836892580785</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1282599111274996</v>
+        <v>0.1277333619569271</v>
       </c>
       <c r="C60">
-        <v>39.21736405130427</v>
+        <v>38.4371486108913</v>
       </c>
       <c r="D60">
-        <v>70.41136405130426</v>
+        <v>70.47414861089129</v>
       </c>
       <c r="E60">
-        <v>21.694</v>
+        <v>22.537</v>
       </c>
       <c r="F60">
-        <v>48.894</v>
+        <v>49.73699999999999</v>
       </c>
       <c r="G60">
         <v>17.7</v>
@@ -6207,28 +6207,28 @@
         <v>154.1</v>
       </c>
       <c r="M60">
-        <v>2.4593682</v>
+        <v>2.5017711</v>
       </c>
       <c r="N60">
-        <v>151.6406318</v>
+        <v>151.5982289</v>
       </c>
       <c r="O60">
-        <v>53.07422113</v>
+        <v>53.05938011499999</v>
       </c>
       <c r="P60">
-        <v>98.56641067</v>
+        <v>98.538848785</v>
       </c>
       <c r="Q60">
-        <v>113.16641067</v>
+        <v>113.138848785</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2602305026845228</v>
+        <v>0.2644958828217734</v>
       </c>
       <c r="T60">
-        <v>1.31143026109716</v>
+        <v>1.337516795041926</v>
       </c>
       <c r="U60">
         <v>0.0503</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>62.65836892580786</v>
+        <v>61.59636267282806</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1277333619569271</v>
+        <v>0.1272068127863547</v>
       </c>
       <c r="C61">
-        <v>38.4371486108913</v>
+        <v>37.65704523815475</v>
       </c>
       <c r="D61">
-        <v>70.47414861089129</v>
+        <v>70.53704523815475</v>
       </c>
       <c r="E61">
-        <v>22.537</v>
+        <v>23.38</v>
       </c>
       <c r="F61">
-        <v>49.73699999999999</v>
+        <v>50.58</v>
       </c>
       <c r="G61">
         <v>17.7</v>
@@ -6289,28 +6289,28 @@
         <v>154.1</v>
       </c>
       <c r="M61">
-        <v>2.5017711</v>
+        <v>2.544174</v>
       </c>
       <c r="N61">
-        <v>151.5982289</v>
+        <v>151.555826</v>
       </c>
       <c r="O61">
-        <v>53.05938011499999</v>
+        <v>53.04453909999999</v>
       </c>
       <c r="P61">
-        <v>98.538848785</v>
+        <v>98.5112869</v>
       </c>
       <c r="Q61">
-        <v>113.138848785</v>
+        <v>113.1112869</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2644958828217734</v>
+        <v>0.2689745319658867</v>
       </c>
       <c r="T61">
-        <v>1.337516795041926</v>
+        <v>1.364907655683932</v>
       </c>
       <c r="U61">
         <v>0.0503</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>61.59636267282806</v>
+        <v>60.56975662828093</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1272068127863547</v>
+        <v>0.1266802636157822</v>
       </c>
       <c r="C62">
-        <v>37.65704523815475</v>
+        <v>36.87705423341651</v>
       </c>
       <c r="D62">
-        <v>70.53704523815475</v>
+        <v>70.6000542334165</v>
       </c>
       <c r="E62">
-        <v>23.38</v>
+        <v>24.223</v>
       </c>
       <c r="F62">
-        <v>50.58</v>
+        <v>51.42299999999999</v>
       </c>
       <c r="G62">
         <v>17.7</v>
@@ -6371,28 +6371,28 @@
         <v>154.1</v>
       </c>
       <c r="M62">
-        <v>2.544174</v>
+        <v>2.586576899999999</v>
       </c>
       <c r="N62">
-        <v>151.555826</v>
+        <v>151.5134231</v>
       </c>
       <c r="O62">
-        <v>53.04453909999999</v>
+        <v>53.02969808499999</v>
       </c>
       <c r="P62">
-        <v>98.5112869</v>
+        <v>98.48372501499999</v>
       </c>
       <c r="Q62">
-        <v>113.1112869</v>
+        <v>113.083725015</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2689745319658867</v>
+        <v>0.2736828554250826</v>
       </c>
       <c r="T62">
-        <v>1.364907655683932</v>
+        <v>1.39370317584604</v>
       </c>
       <c r="U62">
         <v>0.0503</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>60.56975662828093</v>
+        <v>59.57680979830911</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1266802636157822</v>
+        <v>0.1261537144452098</v>
       </c>
       <c r="C63">
-        <v>36.87705423341651</v>
+        <v>36.09717589807241</v>
       </c>
       <c r="D63">
-        <v>70.6000542334165</v>
+        <v>70.66317589807241</v>
       </c>
       <c r="E63">
-        <v>24.223</v>
+        <v>25.066</v>
       </c>
       <c r="F63">
-        <v>51.42299999999999</v>
+        <v>52.266</v>
       </c>
       <c r="G63">
         <v>17.7</v>
@@ -6453,28 +6453,28 @@
         <v>154.1</v>
       </c>
       <c r="M63">
-        <v>2.586576899999999</v>
+        <v>2.6289798</v>
       </c>
       <c r="N63">
-        <v>151.5134231</v>
+        <v>151.4710202</v>
       </c>
       <c r="O63">
-        <v>53.02969808499999</v>
+        <v>53.01485707</v>
       </c>
       <c r="P63">
-        <v>98.48372501499999</v>
+        <v>98.45616312999999</v>
       </c>
       <c r="Q63">
-        <v>113.083725015</v>
+        <v>113.05616313</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2736828554250826</v>
+        <v>0.278638985382131</v>
       </c>
       <c r="T63">
-        <v>1.39370317584604</v>
+        <v>1.424014249700891</v>
       </c>
       <c r="U63">
         <v>0.0503</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>59.57680979830911</v>
+        <v>58.61589351123961</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1261537144452098</v>
+        <v>0.1256271652746373</v>
       </c>
       <c r="C64">
-        <v>36.09717589807241</v>
+        <v>35.31741053459722</v>
       </c>
       <c r="D64">
-        <v>70.66317589807241</v>
+        <v>70.72641053459722</v>
       </c>
       <c r="E64">
-        <v>25.066</v>
+        <v>25.909</v>
       </c>
       <c r="F64">
-        <v>52.266</v>
+        <v>53.109</v>
       </c>
       <c r="G64">
         <v>17.7</v>
@@ -6535,28 +6535,28 @@
         <v>154.1</v>
       </c>
       <c r="M64">
-        <v>2.6289798</v>
+        <v>2.6713827</v>
       </c>
       <c r="N64">
-        <v>151.4710202</v>
+        <v>151.4286173</v>
       </c>
       <c r="O64">
-        <v>53.01485707</v>
+        <v>53.00001605499999</v>
       </c>
       <c r="P64">
-        <v>98.45616312999999</v>
+        <v>98.428601245</v>
       </c>
       <c r="Q64">
-        <v>113.05616313</v>
+        <v>113.028601245</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.278638985382131</v>
+        <v>0.2838630142557765</v>
       </c>
       <c r="T64">
-        <v>1.424014249700891</v>
+        <v>1.455963759980328</v>
       </c>
       <c r="U64">
         <v>0.0503</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>58.61589351123961</v>
+        <v>57.68548250312468</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1256271652746373</v>
+        <v>0.1251006161040649</v>
       </c>
       <c r="C65">
-        <v>35.31741053459722</v>
+        <v>34.53775844654932</v>
       </c>
       <c r="D65">
-        <v>70.72641053459722</v>
+        <v>70.78975844654931</v>
       </c>
       <c r="E65">
-        <v>25.909</v>
+        <v>26.752</v>
       </c>
       <c r="F65">
-        <v>53.109</v>
+        <v>53.952</v>
       </c>
       <c r="G65">
         <v>17.7</v>
@@ -6617,28 +6617,28 @@
         <v>154.1</v>
       </c>
       <c r="M65">
-        <v>2.6713827</v>
+        <v>2.7137856</v>
       </c>
       <c r="N65">
-        <v>151.4286173</v>
+        <v>151.3862144</v>
       </c>
       <c r="O65">
-        <v>53.00001605499999</v>
+        <v>52.98517503999999</v>
       </c>
       <c r="P65">
-        <v>98.428601245</v>
+        <v>98.40103936</v>
       </c>
       <c r="Q65">
-        <v>113.028601245</v>
+        <v>113.00103936</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2838630142557765</v>
+        <v>0.2893772669557357</v>
       </c>
       <c r="T65">
-        <v>1.455963759980328</v>
+        <v>1.489688243053068</v>
       </c>
       <c r="U65">
         <v>0.0503</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>57.68548250312468</v>
+        <v>56.78414683901338</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1251006161040649</v>
+        <v>0.1245740669334924</v>
       </c>
       <c r="C66">
-        <v>34.53775844654932</v>
+        <v>33.75821993857564</v>
       </c>
       <c r="D66">
-        <v>70.78975844654931</v>
+        <v>70.85321993857563</v>
       </c>
       <c r="E66">
-        <v>26.752</v>
+        <v>27.595</v>
       </c>
       <c r="F66">
-        <v>53.952</v>
+        <v>54.795</v>
       </c>
       <c r="G66">
         <v>17.7</v>
@@ -6699,28 +6699,28 @@
         <v>154.1</v>
       </c>
       <c r="M66">
-        <v>2.7137856</v>
+        <v>2.7561885</v>
       </c>
       <c r="N66">
-        <v>151.3862144</v>
+        <v>151.3438115</v>
       </c>
       <c r="O66">
-        <v>52.98517503999999</v>
+        <v>52.97033402499999</v>
       </c>
       <c r="P66">
-        <v>98.40103936</v>
+        <v>98.37347747499999</v>
       </c>
       <c r="Q66">
-        <v>113.00103936</v>
+        <v>112.973477475</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2893772669557357</v>
+        <v>0.2952066198099783</v>
       </c>
       <c r="T66">
-        <v>1.489688243053068</v>
+        <v>1.52533983944425</v>
       </c>
       <c r="U66">
         <v>0.0503</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>56.78414683901338</v>
+        <v>55.91054457995162</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1245740669334924</v>
+        <v>0.1240475177629199</v>
       </c>
       <c r="C67">
-        <v>33.75821993857564</v>
+        <v>32.97879531641652</v>
       </c>
       <c r="D67">
-        <v>70.85321993857563</v>
+        <v>70.91679531641651</v>
       </c>
       <c r="E67">
-        <v>27.595</v>
+        <v>28.438</v>
       </c>
       <c r="F67">
-        <v>54.795</v>
+        <v>55.638</v>
       </c>
       <c r="G67">
         <v>17.7</v>
@@ -6781,28 +6781,28 @@
         <v>154.1</v>
       </c>
       <c r="M67">
-        <v>2.7561885</v>
+        <v>2.7985914</v>
       </c>
       <c r="N67">
-        <v>151.3438115</v>
+        <v>151.3014086</v>
       </c>
       <c r="O67">
-        <v>52.97033402499999</v>
+        <v>52.95549301</v>
       </c>
       <c r="P67">
-        <v>98.37347747499999</v>
+        <v>98.34591559</v>
       </c>
       <c r="Q67">
-        <v>112.973477475</v>
+        <v>112.94591559</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2952066198099783</v>
+        <v>0.3013788757732939</v>
       </c>
       <c r="T67">
-        <v>1.52533983944425</v>
+        <v>1.563088588564324</v>
       </c>
       <c r="U67">
         <v>0.0503</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>55.91054457995162</v>
+        <v>55.06341511661903</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1240475177629199</v>
+        <v>0.1235209685923475</v>
       </c>
       <c r="C68">
-        <v>32.97879531641652</v>
+        <v>32.19948488691066</v>
       </c>
       <c r="D68">
-        <v>70.91679531641651</v>
+        <v>70.98048488691066</v>
       </c>
       <c r="E68">
-        <v>28.438</v>
+        <v>29.281</v>
       </c>
       <c r="F68">
-        <v>55.638</v>
+        <v>56.481</v>
       </c>
       <c r="G68">
         <v>17.7</v>
@@ -6863,28 +6863,28 @@
         <v>154.1</v>
       </c>
       <c r="M68">
-        <v>2.7985914</v>
+        <v>2.8409943</v>
       </c>
       <c r="N68">
-        <v>151.3014086</v>
+        <v>151.2590057</v>
       </c>
       <c r="O68">
-        <v>52.95549301</v>
+        <v>52.940651995</v>
       </c>
       <c r="P68">
-        <v>98.34591559</v>
+        <v>98.31835370499999</v>
       </c>
       <c r="Q68">
-        <v>112.94591559</v>
+        <v>112.918353705</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3013788757732939</v>
+        <v>0.3079252078555985</v>
       </c>
       <c r="T68">
-        <v>1.563088588564324</v>
+        <v>1.603125140661374</v>
       </c>
       <c r="U68">
         <v>0.0503</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>55.06341511661903</v>
+        <v>54.24157309995307</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1235209685923475</v>
+        <v>0.122994419421775</v>
       </c>
       <c r="C69">
-        <v>32.19948488691066</v>
+        <v>31.42028895799999</v>
       </c>
       <c r="D69">
-        <v>70.98048488691066</v>
+        <v>71.044288958</v>
       </c>
       <c r="E69">
-        <v>29.281</v>
+        <v>30.12400000000001</v>
       </c>
       <c r="F69">
-        <v>56.481</v>
+        <v>57.32400000000001</v>
       </c>
       <c r="G69">
         <v>17.7</v>
@@ -6945,28 +6945,28 @@
         <v>154.1</v>
       </c>
       <c r="M69">
-        <v>2.8409943</v>
+        <v>2.8833972</v>
       </c>
       <c r="N69">
-        <v>151.2590057</v>
+        <v>151.2166028</v>
       </c>
       <c r="O69">
-        <v>52.940651995</v>
+        <v>52.92581098</v>
       </c>
       <c r="P69">
-        <v>98.31835370499999</v>
+        <v>98.29079182000001</v>
       </c>
       <c r="Q69">
-        <v>112.918353705</v>
+        <v>112.89079182</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3079252078555985</v>
+        <v>0.314880685693047</v>
       </c>
       <c r="T69">
-        <v>1.603125140661374</v>
+        <v>1.645663977264488</v>
       </c>
       <c r="U69">
         <v>0.0503</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>54.24157309995307</v>
+        <v>53.4439029073067</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.122994419421775</v>
+        <v>0.1224678702512026</v>
       </c>
       <c r="C70">
-        <v>31.42028895799999</v>
+        <v>30.64120783873469</v>
       </c>
       <c r="D70">
-        <v>71.044288958</v>
+        <v>71.10820783873469</v>
       </c>
       <c r="E70">
-        <v>30.12400000000001</v>
+        <v>30.967</v>
       </c>
       <c r="F70">
-        <v>57.32400000000001</v>
+        <v>58.167</v>
       </c>
       <c r="G70">
         <v>17.7</v>
@@ -7027,28 +7027,28 @@
         <v>154.1</v>
       </c>
       <c r="M70">
-        <v>2.8833972</v>
+        <v>2.9258001</v>
       </c>
       <c r="N70">
-        <v>151.2166028</v>
+        <v>151.1741999</v>
       </c>
       <c r="O70">
-        <v>52.92581098</v>
+        <v>52.91096996499999</v>
       </c>
       <c r="P70">
-        <v>98.29079182000001</v>
+        <v>98.263229935</v>
       </c>
       <c r="Q70">
-        <v>112.89079182</v>
+        <v>112.863229935</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.314880685693047</v>
+        <v>0.3222849040361374</v>
       </c>
       <c r="T70">
-        <v>1.645663977264488</v>
+        <v>1.690947254938771</v>
       </c>
       <c r="U70">
         <v>0.0503</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>53.4439029073067</v>
+        <v>52.6693535898095</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1224678702512026</v>
+        <v>0.1219413210806301</v>
       </c>
       <c r="C71">
-        <v>30.64120783873469</v>
+        <v>29.86224183927817</v>
       </c>
       <c r="D71">
-        <v>71.10820783873469</v>
+        <v>71.17224183927817</v>
       </c>
       <c r="E71">
-        <v>30.967</v>
+        <v>31.81000000000001</v>
       </c>
       <c r="F71">
-        <v>58.167</v>
+        <v>59.01000000000001</v>
       </c>
       <c r="G71">
         <v>17.7</v>
@@ -7109,28 +7109,28 @@
         <v>154.1</v>
       </c>
       <c r="M71">
-        <v>2.9258001</v>
+        <v>2.968203</v>
       </c>
       <c r="N71">
-        <v>151.1741999</v>
+        <v>151.131797</v>
       </c>
       <c r="O71">
-        <v>52.91096996499999</v>
+        <v>52.89612895</v>
       </c>
       <c r="P71">
-        <v>98.263229935</v>
+        <v>98.23566805000002</v>
       </c>
       <c r="Q71">
-        <v>112.863229935</v>
+        <v>112.83566805</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3222849040361374</v>
+        <v>0.3301827369354337</v>
       </c>
       <c r="T71">
-        <v>1.690947254938771</v>
+        <v>1.73924941779134</v>
       </c>
       <c r="U71">
         <v>0.0503</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>52.6693535898095</v>
+        <v>51.91693425281223</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1219413210806301</v>
+        <v>0.1214147719100576</v>
       </c>
       <c r="C72">
-        <v>29.86224183927817</v>
+        <v>29.08339127091201</v>
       </c>
       <c r="D72">
-        <v>71.17224183927817</v>
+        <v>71.23639127091201</v>
       </c>
       <c r="E72">
-        <v>31.81000000000001</v>
+        <v>32.65300000000001</v>
       </c>
       <c r="F72">
-        <v>59.01000000000001</v>
+        <v>59.853</v>
       </c>
       <c r="G72">
         <v>17.7</v>
@@ -7191,28 +7191,28 @@
         <v>154.1</v>
       </c>
       <c r="M72">
-        <v>2.968203</v>
+        <v>3.0106059</v>
       </c>
       <c r="N72">
-        <v>151.131797</v>
+        <v>151.0893941</v>
       </c>
       <c r="O72">
-        <v>52.89612895</v>
+        <v>52.881287935</v>
       </c>
       <c r="P72">
-        <v>98.23566805000002</v>
+        <v>98.208106165</v>
       </c>
       <c r="Q72">
-        <v>112.83566805</v>
+        <v>112.808106165</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3301827369354337</v>
+        <v>0.3386252479657161</v>
       </c>
       <c r="T72">
-        <v>1.73924941779134</v>
+        <v>1.790882764288914</v>
       </c>
       <c r="U72">
         <v>0.0503</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>51.91693425281223</v>
+        <v>51.18570982671628</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1214147719100576</v>
+        <v>0.1208882227394852</v>
       </c>
       <c r="C73">
-        <v>29.08339127091202</v>
+        <v>28.30465644604112</v>
       </c>
       <c r="D73">
-        <v>71.23639127091201</v>
+        <v>71.30065644604112</v>
       </c>
       <c r="E73">
-        <v>32.65299999999999</v>
+        <v>33.496</v>
       </c>
       <c r="F73">
-        <v>59.85299999999999</v>
+        <v>60.696</v>
       </c>
       <c r="G73">
         <v>17.7</v>
@@ -7273,28 +7273,28 @@
         <v>154.1</v>
       </c>
       <c r="M73">
-        <v>3.010605899999999</v>
+        <v>3.0530088</v>
       </c>
       <c r="N73">
-        <v>151.0893941</v>
+        <v>151.0469912</v>
       </c>
       <c r="O73">
-        <v>52.881287935</v>
+        <v>52.86644692</v>
       </c>
       <c r="P73">
-        <v>98.208106165</v>
+        <v>98.18054428000001</v>
       </c>
       <c r="Q73">
-        <v>112.808106165</v>
+        <v>112.78054428</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.338625247965716</v>
+        <v>0.3476707954981614</v>
       </c>
       <c r="T73">
-        <v>1.790882764288913</v>
+        <v>1.846204206964885</v>
       </c>
       <c r="U73">
         <v>0.0503</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>51.18570982671628</v>
+        <v>50.47479719023411</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1208882227394852</v>
+        <v>0.1203616735689128</v>
       </c>
       <c r="C74">
-        <v>28.30465644604112</v>
+        <v>27.52603767819878</v>
       </c>
       <c r="D74">
-        <v>71.30065644604112</v>
+        <v>71.36503767819877</v>
       </c>
       <c r="E74">
-        <v>33.496</v>
+        <v>34.339</v>
       </c>
       <c r="F74">
-        <v>60.696</v>
+        <v>61.53899999999999</v>
       </c>
       <c r="G74">
         <v>17.7</v>
@@ -7355,28 +7355,28 @@
         <v>154.1</v>
       </c>
       <c r="M74">
-        <v>3.0530088</v>
+        <v>3.0954117</v>
       </c>
       <c r="N74">
-        <v>151.0469912</v>
+        <v>151.0045883</v>
       </c>
       <c r="O74">
-        <v>52.86644692</v>
+        <v>52.85160590499999</v>
       </c>
       <c r="P74">
-        <v>98.18054428000001</v>
+        <v>98.15298239500001</v>
       </c>
       <c r="Q74">
-        <v>112.78054428</v>
+        <v>112.752982395</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3476707954981614</v>
+        <v>0.3573863835885657</v>
       </c>
       <c r="T74">
-        <v>1.846204206964885</v>
+        <v>1.905623534283521</v>
       </c>
       <c r="U74">
         <v>0.0503</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>50.47479719023411</v>
+        <v>49.7833616122857</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1203616735689128</v>
+        <v>0.1198351243983403</v>
       </c>
       <c r="C75">
-        <v>27.52603767819878</v>
+        <v>26.74753528205165</v>
       </c>
       <c r="D75">
-        <v>71.36503767819877</v>
+        <v>71.42953528205165</v>
       </c>
       <c r="E75">
-        <v>34.339</v>
+        <v>35.182</v>
       </c>
       <c r="F75">
-        <v>61.53899999999999</v>
+        <v>62.382</v>
       </c>
       <c r="G75">
         <v>17.7</v>
@@ -7437,28 +7437,28 @@
         <v>154.1</v>
       </c>
       <c r="M75">
-        <v>3.0954117</v>
+        <v>3.1378146</v>
       </c>
       <c r="N75">
-        <v>151.0045883</v>
+        <v>150.9621854</v>
       </c>
       <c r="O75">
-        <v>52.85160590499999</v>
+        <v>52.83676488999999</v>
       </c>
       <c r="P75">
-        <v>98.15298239500001</v>
+        <v>98.12542051</v>
       </c>
       <c r="Q75">
-        <v>112.752982395</v>
+        <v>112.72542051</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3573863835885657</v>
+        <v>0.367849324609001</v>
       </c>
       <c r="T75">
-        <v>1.905623534283521</v>
+        <v>1.969613579088205</v>
       </c>
       <c r="U75">
         <v>0.0503</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>49.7833616122857</v>
+        <v>49.11061348238994</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1198351243983403</v>
+        <v>0.1193085752277678</v>
       </c>
       <c r="C76">
-        <v>26.74753528205165</v>
+        <v>25.96914957340502</v>
       </c>
       <c r="D76">
-        <v>71.42953528205165</v>
+        <v>71.49414957340501</v>
       </c>
       <c r="E76">
-        <v>35.182</v>
+        <v>36.02499999999999</v>
       </c>
       <c r="F76">
-        <v>62.382</v>
+        <v>63.22499999999999</v>
       </c>
       <c r="G76">
         <v>17.7</v>
@@ -7519,28 +7519,28 @@
         <v>154.1</v>
       </c>
       <c r="M76">
-        <v>3.1378146</v>
+        <v>3.180217499999999</v>
       </c>
       <c r="N76">
-        <v>150.9621854</v>
+        <v>150.9197825</v>
       </c>
       <c r="O76">
-        <v>52.83676488999999</v>
+        <v>52.821923875</v>
       </c>
       <c r="P76">
-        <v>98.12542051</v>
+        <v>98.097858625</v>
       </c>
       <c r="Q76">
-        <v>112.72542051</v>
+        <v>112.697858625</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.367849324609001</v>
+        <v>0.3791493009110713</v>
       </c>
       <c r="T76">
-        <v>1.969613579088205</v>
+        <v>2.038722827477266</v>
       </c>
       <c r="U76">
         <v>0.0503</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>49.11061348238994</v>
+        <v>48.45580530262475</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1193085752277678</v>
+        <v>0.1187820260571954</v>
       </c>
       <c r="C77">
-        <v>25.96914957340502</v>
+        <v>25.1908808692079</v>
       </c>
       <c r="D77">
-        <v>71.49414957340501</v>
+        <v>71.5588808692079</v>
       </c>
       <c r="E77">
-        <v>36.02499999999999</v>
+        <v>36.86799999999999</v>
       </c>
       <c r="F77">
-        <v>63.22499999999999</v>
+        <v>64.068</v>
       </c>
       <c r="G77">
         <v>17.7</v>
@@ -7601,28 +7601,28 @@
         <v>154.1</v>
       </c>
       <c r="M77">
-        <v>3.180217499999999</v>
+        <v>3.2226204</v>
       </c>
       <c r="N77">
-        <v>150.9197825</v>
+        <v>150.8773796</v>
       </c>
       <c r="O77">
-        <v>52.821923875</v>
+        <v>52.80708285999999</v>
       </c>
       <c r="P77">
-        <v>98.097858625</v>
+        <v>98.07029673999999</v>
       </c>
       <c r="Q77">
-        <v>112.697858625</v>
+        <v>112.67029674</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3791493009110713</v>
+        <v>0.3913909419049807</v>
       </c>
       <c r="T77">
-        <v>2.038722827477266</v>
+        <v>2.113591179898747</v>
       </c>
       <c r="U77">
         <v>0.0503</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>48.45580530262475</v>
+        <v>47.81822891706388</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1187820260571954</v>
+        <v>0.1182554768866229</v>
       </c>
       <c r="C78">
-        <v>25.1908808692079</v>
+        <v>24.4127294875582</v>
       </c>
       <c r="D78">
-        <v>71.5588808692079</v>
+        <v>71.62372948755819</v>
       </c>
       <c r="E78">
-        <v>36.86799999999999</v>
+        <v>37.711</v>
       </c>
       <c r="F78">
-        <v>64.068</v>
+        <v>64.911</v>
       </c>
       <c r="G78">
         <v>17.7</v>
@@ -7683,28 +7683,28 @@
         <v>154.1</v>
       </c>
       <c r="M78">
-        <v>3.2226204</v>
+        <v>3.2650233</v>
       </c>
       <c r="N78">
-        <v>150.8773796</v>
+        <v>150.8349767</v>
       </c>
       <c r="O78">
-        <v>52.80708285999999</v>
+        <v>52.792241845</v>
       </c>
       <c r="P78">
-        <v>98.07029673999999</v>
+        <v>98.04273485499999</v>
       </c>
       <c r="Q78">
-        <v>112.67029674</v>
+        <v>112.642734855</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3913909419049807</v>
+        <v>0.4046970734200996</v>
       </c>
       <c r="T78">
-        <v>2.113591179898747</v>
+        <v>2.19496982383514</v>
       </c>
       <c r="U78">
         <v>0.0503</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>47.81822891706388</v>
+        <v>47.19721295710202</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1182554768866229</v>
+        <v>0.1177289277160504</v>
       </c>
       <c r="C79">
-        <v>24.4127294875582</v>
+        <v>23.63469574770791</v>
       </c>
       <c r="D79">
-        <v>71.62372948755819</v>
+        <v>71.68869574770791</v>
       </c>
       <c r="E79">
-        <v>37.711</v>
+        <v>38.554</v>
       </c>
       <c r="F79">
-        <v>64.911</v>
+        <v>65.754</v>
       </c>
       <c r="G79">
         <v>17.7</v>
@@ -7765,28 +7765,28 @@
         <v>154.1</v>
       </c>
       <c r="M79">
-        <v>3.2650233</v>
+        <v>3.3074262</v>
       </c>
       <c r="N79">
-        <v>150.8349767</v>
+        <v>150.7925738</v>
       </c>
       <c r="O79">
-        <v>52.792241845</v>
+        <v>52.77740082999999</v>
       </c>
       <c r="P79">
-        <v>98.04273485499999</v>
+        <v>98.01517296999999</v>
       </c>
       <c r="Q79">
-        <v>112.642734855</v>
+        <v>112.61517297</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4046970734200996</v>
+        <v>0.4192128532547748</v>
       </c>
       <c r="T79">
-        <v>2.19496982383514</v>
+        <v>2.283746526311205</v>
       </c>
       <c r="U79">
         <v>0.0503</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>47.19721295710202</v>
+        <v>46.59212048329302</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1177289277160504</v>
+        <v>0.117202378545478</v>
       </c>
       <c r="C80">
-        <v>23.63469574770791</v>
+        <v>22.85677997006852</v>
       </c>
       <c r="D80">
-        <v>71.68869574770791</v>
+        <v>71.75377997006851</v>
       </c>
       <c r="E80">
-        <v>38.554</v>
+        <v>39.39699999999999</v>
       </c>
       <c r="F80">
-        <v>65.754</v>
+        <v>66.59699999999999</v>
       </c>
       <c r="G80">
         <v>17.7</v>
@@ -7847,28 +7847,28 @@
         <v>154.1</v>
       </c>
       <c r="M80">
-        <v>3.3074262</v>
+        <v>3.3498291</v>
       </c>
       <c r="N80">
-        <v>150.7925738</v>
+        <v>150.7501709</v>
       </c>
       <c r="O80">
-        <v>52.77740082999999</v>
+        <v>52.762559815</v>
       </c>
       <c r="P80">
-        <v>98.01517296999999</v>
+        <v>97.987611085</v>
       </c>
       <c r="Q80">
-        <v>112.61517297</v>
+        <v>112.587611085</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4192128532547748</v>
+        <v>0.4351110883118</v>
       </c>
       <c r="T80">
-        <v>2.283746526311205</v>
+        <v>2.38097815283261</v>
       </c>
       <c r="U80">
         <v>0.0503</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>46.59212048329302</v>
+        <v>46.00234680628932</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.117202378545478</v>
+        <v>0.1166758293749055</v>
       </c>
       <c r="C81">
-        <v>22.85677997006852</v>
+        <v>22.07898247621597</v>
       </c>
       <c r="D81">
-        <v>71.75377997006851</v>
+        <v>71.81898247621596</v>
       </c>
       <c r="E81">
-        <v>39.39699999999999</v>
+        <v>40.23999999999999</v>
       </c>
       <c r="F81">
-        <v>66.59699999999999</v>
+        <v>67.44</v>
       </c>
       <c r="G81">
         <v>17.7</v>
@@ -7929,28 +7929,28 @@
         <v>154.1</v>
       </c>
       <c r="M81">
-        <v>3.3498291</v>
+        <v>3.392232</v>
       </c>
       <c r="N81">
-        <v>150.7501709</v>
+        <v>150.707768</v>
       </c>
       <c r="O81">
-        <v>52.762559815</v>
+        <v>52.74771879999999</v>
       </c>
       <c r="P81">
-        <v>97.987611085</v>
+        <v>97.96004919999999</v>
       </c>
       <c r="Q81">
-        <v>112.587611085</v>
+        <v>112.5600492</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4351110883118</v>
+        <v>0.4525991468745277</v>
       </c>
       <c r="T81">
-        <v>2.38097815283261</v>
+        <v>2.487932942006155</v>
       </c>
       <c r="U81">
         <v>0.0503</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>46.00234680628932</v>
+        <v>45.42731747121069</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1166758293749055</v>
+        <v>0.1161492802043331</v>
       </c>
       <c r="C82">
-        <v>22.07898247621597</v>
+        <v>21.30130358889625</v>
       </c>
       <c r="D82">
-        <v>71.81898247621596</v>
+        <v>71.88430358889624</v>
       </c>
       <c r="E82">
-        <v>40.23999999999999</v>
+        <v>41.083</v>
       </c>
       <c r="F82">
-        <v>67.44</v>
+        <v>68.283</v>
       </c>
       <c r="G82">
         <v>17.7</v>
@@ -8011,28 +8011,28 @@
         <v>154.1</v>
       </c>
       <c r="M82">
-        <v>3.392232</v>
+        <v>3.4346349</v>
       </c>
       <c r="N82">
-        <v>150.707768</v>
+        <v>150.6653651</v>
       </c>
       <c r="O82">
-        <v>52.74771879999999</v>
+        <v>52.732877785</v>
       </c>
       <c r="P82">
-        <v>97.96004919999999</v>
+        <v>97.932487315</v>
       </c>
       <c r="Q82">
-        <v>112.5600492</v>
+        <v>112.532487315</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4525991468745277</v>
+        <v>0.4719280537070163</v>
       </c>
       <c r="T82">
-        <v>2.487932942006155</v>
+        <v>2.606146130040074</v>
       </c>
       <c r="U82">
         <v>0.0503</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>45.42731747121069</v>
+        <v>44.86648639131921</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1161492802043331</v>
+        <v>0.1156227310337606</v>
       </c>
       <c r="C83">
-        <v>21.30130358889625</v>
+        <v>20.52374363203053</v>
       </c>
       <c r="D83">
-        <v>71.88430358889624</v>
+        <v>71.94974363203053</v>
       </c>
       <c r="E83">
-        <v>41.083</v>
+        <v>41.926</v>
       </c>
       <c r="F83">
-        <v>68.283</v>
+        <v>69.126</v>
       </c>
       <c r="G83">
         <v>17.7</v>
@@ -8093,28 +8093,28 @@
         <v>154.1</v>
       </c>
       <c r="M83">
-        <v>3.4346349</v>
+        <v>3.4770378</v>
       </c>
       <c r="N83">
-        <v>150.6653651</v>
+        <v>150.6229622</v>
       </c>
       <c r="O83">
-        <v>52.732877785</v>
+        <v>52.71803676999999</v>
       </c>
       <c r="P83">
-        <v>97.932487315</v>
+        <v>97.90492542999999</v>
       </c>
       <c r="Q83">
-        <v>112.532487315</v>
+        <v>112.50492543</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4719280537070163</v>
+        <v>0.4934046168542257</v>
       </c>
       <c r="T83">
-        <v>2.606146130040074</v>
+        <v>2.737494116744427</v>
       </c>
       <c r="U83">
         <v>0.0503</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>44.86648639131921</v>
+        <v>44.31933411825433</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1156227310337606</v>
+        <v>0.1150961818631882</v>
       </c>
       <c r="C84">
-        <v>20.52374363203053</v>
+        <v>19.74630293072065</v>
       </c>
       <c r="D84">
-        <v>71.94974363203053</v>
+        <v>72.01530293072065</v>
       </c>
       <c r="E84">
-        <v>41.926</v>
+        <v>42.76900000000001</v>
       </c>
       <c r="F84">
-        <v>69.126</v>
+        <v>69.96900000000001</v>
       </c>
       <c r="G84">
         <v>17.7</v>
@@ -8175,28 +8175,28 @@
         <v>154.1</v>
       </c>
       <c r="M84">
-        <v>3.4770378</v>
+        <v>3.5194407</v>
       </c>
       <c r="N84">
-        <v>150.6229622</v>
+        <v>150.5805593</v>
       </c>
       <c r="O84">
-        <v>52.71803676999999</v>
+        <v>52.703195755</v>
       </c>
       <c r="P84">
-        <v>97.90492542999999</v>
+        <v>97.87736354500001</v>
       </c>
       <c r="Q84">
-        <v>112.50492543</v>
+        <v>112.477363545</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4934046168542257</v>
+        <v>0.5174078344893424</v>
       </c>
       <c r="T84">
-        <v>2.737494116744427</v>
+        <v>2.884294807766941</v>
       </c>
       <c r="U84">
         <v>0.0503</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>44.31933411825433</v>
+        <v>43.78536623731151</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1150961818631882</v>
+        <v>0.1145696326926157</v>
       </c>
       <c r="C85">
-        <v>19.74630293072065</v>
+        <v>18.96898181125439</v>
       </c>
       <c r="D85">
-        <v>72.01530293072065</v>
+        <v>72.08098181125439</v>
       </c>
       <c r="E85">
-        <v>42.76900000000001</v>
+        <v>43.61199999999999</v>
       </c>
       <c r="F85">
-        <v>69.96900000000001</v>
+        <v>70.812</v>
       </c>
       <c r="G85">
         <v>17.7</v>
@@ -8257,28 +8257,28 @@
         <v>154.1</v>
       </c>
       <c r="M85">
-        <v>3.5194407</v>
+        <v>3.5618436</v>
       </c>
       <c r="N85">
-        <v>150.5805593</v>
+        <v>150.5381564</v>
       </c>
       <c r="O85">
-        <v>52.703195755</v>
+        <v>52.68835473999999</v>
       </c>
       <c r="P85">
-        <v>97.87736354500001</v>
+        <v>97.84980166</v>
       </c>
       <c r="Q85">
-        <v>112.477363545</v>
+        <v>112.44980166</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5174078344893424</v>
+        <v>0.5444114543288483</v>
       </c>
       <c r="T85">
-        <v>2.884294807766941</v>
+        <v>3.049445585167267</v>
       </c>
       <c r="U85">
         <v>0.0503</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>43.78536623731151</v>
+        <v>43.26411187734352</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1145696326926157</v>
+        <v>0.1140430835220433</v>
       </c>
       <c r="C86">
-        <v>18.96898181125439</v>
+        <v>18.19178060111093</v>
       </c>
       <c r="D86">
-        <v>72.08098181125439</v>
+        <v>72.14678060111093</v>
       </c>
       <c r="E86">
-        <v>43.61199999999999</v>
+        <v>44.455</v>
       </c>
       <c r="F86">
-        <v>70.812</v>
+        <v>71.655</v>
       </c>
       <c r="G86">
         <v>17.7</v>
@@ -8339,28 +8339,28 @@
         <v>154.1</v>
       </c>
       <c r="M86">
-        <v>3.5618436</v>
+        <v>3.6042465</v>
       </c>
       <c r="N86">
-        <v>150.5381564</v>
+        <v>150.4957535</v>
       </c>
       <c r="O86">
-        <v>52.68835473999999</v>
+        <v>52.673513725</v>
       </c>
       <c r="P86">
-        <v>97.84980166</v>
+        <v>97.82223977500001</v>
       </c>
       <c r="Q86">
-        <v>112.44980166</v>
+        <v>112.422239775</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5444114543288481</v>
+        <v>0.5750155568136216</v>
       </c>
       <c r="T86">
-        <v>3.049445585167266</v>
+        <v>3.23661646622097</v>
       </c>
       <c r="U86">
         <v>0.0503</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>43.26411187734352</v>
+        <v>42.75512232584536</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1140430835220433</v>
+        <v>0.1135165343514708</v>
       </c>
       <c r="C87">
-        <v>18.19178060111093</v>
+        <v>17.41469962896635</v>
       </c>
       <c r="D87">
-        <v>72.14678060111093</v>
+        <v>72.21269962896633</v>
       </c>
       <c r="E87">
-        <v>44.455</v>
+        <v>45.29799999999999</v>
       </c>
       <c r="F87">
-        <v>71.655</v>
+        <v>72.49799999999999</v>
       </c>
       <c r="G87">
         <v>17.7</v>
@@ -8421,28 +8421,28 @@
         <v>154.1</v>
       </c>
       <c r="M87">
-        <v>3.6042465</v>
+        <v>3.646649399999999</v>
       </c>
       <c r="N87">
-        <v>150.4957535</v>
+        <v>150.4533506</v>
       </c>
       <c r="O87">
-        <v>52.673513725</v>
+        <v>52.65867271</v>
       </c>
       <c r="P87">
-        <v>97.82223977500001</v>
+        <v>97.79467789</v>
       </c>
       <c r="Q87">
-        <v>112.422239775</v>
+        <v>112.39467789</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5750155568136216</v>
+        <v>0.6099916739390769</v>
       </c>
       <c r="T87">
-        <v>3.23661646622097</v>
+        <v>3.45052604456806</v>
       </c>
       <c r="U87">
         <v>0.0503</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>42.75512232584536</v>
+        <v>42.25796974066112</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1135165343514708</v>
+        <v>0.1129899851808983</v>
       </c>
       <c r="C88">
-        <v>17.41469962896635</v>
+        <v>16.63773922469893</v>
       </c>
       <c r="D88">
-        <v>72.21269962896633</v>
+        <v>72.27873922469892</v>
       </c>
       <c r="E88">
-        <v>45.29799999999999</v>
+        <v>46.14099999999999</v>
       </c>
       <c r="F88">
-        <v>72.49799999999999</v>
+        <v>73.34099999999999</v>
       </c>
       <c r="G88">
         <v>17.7</v>
@@ -8503,28 +8503,28 @@
         <v>154.1</v>
       </c>
       <c r="M88">
-        <v>3.646649399999999</v>
+        <v>3.6890523</v>
       </c>
       <c r="N88">
-        <v>150.4533506</v>
+        <v>150.4109477</v>
       </c>
       <c r="O88">
-        <v>52.65867271</v>
+        <v>52.643831695</v>
       </c>
       <c r="P88">
-        <v>97.79467789</v>
+        <v>97.76711600500001</v>
       </c>
       <c r="Q88">
-        <v>112.39467789</v>
+        <v>112.367116005</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6099916739390769</v>
+        <v>0.6503487321607563</v>
       </c>
       <c r="T88">
-        <v>3.45052604456806</v>
+        <v>3.697344788814702</v>
       </c>
       <c r="U88">
         <v>0.0503</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>42.25796974066112</v>
+        <v>41.77224595053858</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1129899851808983</v>
+        <v>0.1124634360103259</v>
       </c>
       <c r="C89">
-        <v>16.63773922469893</v>
+        <v>15.86089971939491</v>
       </c>
       <c r="D89">
-        <v>72.27873922469892</v>
+        <v>72.3448997193949</v>
       </c>
       <c r="E89">
-        <v>46.14099999999999</v>
+        <v>46.98399999999999</v>
       </c>
       <c r="F89">
-        <v>73.34099999999999</v>
+        <v>74.184</v>
       </c>
       <c r="G89">
         <v>17.7</v>
@@ -8585,28 +8585,28 @@
         <v>154.1</v>
       </c>
       <c r="M89">
-        <v>3.6890523</v>
+        <v>3.7314552</v>
       </c>
       <c r="N89">
-        <v>150.4109477</v>
+        <v>150.3685448</v>
       </c>
       <c r="O89">
-        <v>52.643831695</v>
+        <v>52.62899067999999</v>
       </c>
       <c r="P89">
-        <v>97.76711600500001</v>
+        <v>97.73955412000001</v>
       </c>
       <c r="Q89">
-        <v>112.367116005</v>
+        <v>112.33955412</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6503487321607563</v>
+        <v>0.6974319667527156</v>
       </c>
       <c r="T89">
-        <v>3.697344788814702</v>
+        <v>3.985299990435785</v>
       </c>
       <c r="U89">
         <v>0.0503</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>41.77224595053858</v>
+        <v>41.29756133746427</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1124634360103259</v>
+        <v>0.1119368868397534</v>
       </c>
       <c r="C90">
-        <v>15.86089971939491</v>
+        <v>15.08418144535378</v>
       </c>
       <c r="D90">
-        <v>72.3448997193949</v>
+        <v>72.41118144535378</v>
       </c>
       <c r="E90">
-        <v>46.98399999999999</v>
+        <v>47.827</v>
       </c>
       <c r="F90">
-        <v>74.184</v>
+        <v>75.027</v>
       </c>
       <c r="G90">
         <v>17.7</v>
@@ -8667,28 +8667,28 @@
         <v>154.1</v>
       </c>
       <c r="M90">
-        <v>3.7314552</v>
+        <v>3.7738581</v>
       </c>
       <c r="N90">
-        <v>150.3685448</v>
+        <v>150.3261419</v>
       </c>
       <c r="O90">
-        <v>52.62899067999999</v>
+        <v>52.61414966499999</v>
       </c>
       <c r="P90">
-        <v>97.73955412000001</v>
+        <v>97.711992235</v>
       </c>
       <c r="Q90">
-        <v>112.33955412</v>
+        <v>112.311992235</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6974319667527156</v>
+        <v>0.7530757894523038</v>
       </c>
       <c r="T90">
-        <v>3.985299990435785</v>
+        <v>4.325610683260702</v>
       </c>
       <c r="U90">
         <v>0.0503</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>41.29756133746427</v>
+        <v>40.83354379434669</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1119368868397534</v>
+        <v>0.111410337669181</v>
       </c>
       <c r="C91">
-        <v>15.08418144535378</v>
+        <v>14.307584736094</v>
       </c>
       <c r="D91">
-        <v>72.41118144535378</v>
+        <v>72.477584736094</v>
       </c>
       <c r="E91">
-        <v>47.827</v>
+        <v>48.67</v>
       </c>
       <c r="F91">
-        <v>75.027</v>
+        <v>75.87</v>
       </c>
       <c r="G91">
         <v>17.7</v>
@@ -8749,28 +8749,28 @@
         <v>154.1</v>
       </c>
       <c r="M91">
-        <v>3.7738581</v>
+        <v>3.816261</v>
       </c>
       <c r="N91">
-        <v>150.3261419</v>
+        <v>150.283739</v>
       </c>
       <c r="O91">
-        <v>52.61414966499999</v>
+        <v>52.59930865</v>
       </c>
       <c r="P91">
-        <v>97.711992235</v>
+        <v>97.68443035</v>
       </c>
       <c r="Q91">
-        <v>112.311992235</v>
+        <v>112.28443035</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7530757894523038</v>
+        <v>0.8198483766918097</v>
       </c>
       <c r="T91">
-        <v>4.325610683260702</v>
+        <v>4.733983514650601</v>
       </c>
       <c r="U91">
         <v>0.0503</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>40.83354379434669</v>
+        <v>40.37983775218729</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.111410337669181</v>
+        <v>0.1108837884986085</v>
       </c>
       <c r="C92">
-        <v>14.307584736094</v>
+        <v>13.53110992635851</v>
       </c>
       <c r="D92">
-        <v>72.477584736094</v>
+        <v>72.5441099263585</v>
       </c>
       <c r="E92">
-        <v>48.67</v>
+        <v>49.51299999999999</v>
       </c>
       <c r="F92">
-        <v>75.87</v>
+        <v>76.71299999999999</v>
       </c>
       <c r="G92">
         <v>17.7</v>
@@ -8831,28 +8831,28 @@
         <v>154.1</v>
       </c>
       <c r="M92">
-        <v>3.816261</v>
+        <v>3.858663899999999</v>
       </c>
       <c r="N92">
-        <v>150.283739</v>
+        <v>150.2413361</v>
       </c>
       <c r="O92">
-        <v>52.59930865</v>
+        <v>52.58446763499999</v>
       </c>
       <c r="P92">
-        <v>97.68443035</v>
+        <v>97.656868465</v>
       </c>
       <c r="Q92">
-        <v>112.28443035</v>
+        <v>112.256868465</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.8198483766918097</v>
+        <v>0.9014593166512057</v>
       </c>
       <c r="T92">
-        <v>4.733983514650601</v>
+        <v>5.233105864127145</v>
       </c>
       <c r="U92">
         <v>0.0503</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>40.37983775218729</v>
+        <v>39.93610327139402</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1108837884986085</v>
+        <v>0.1103572393280361</v>
       </c>
       <c r="C93">
-        <v>13.53110992635851</v>
+        <v>12.75475735212041</v>
       </c>
       <c r="D93">
-        <v>72.5441099263585</v>
+        <v>72.6107573521204</v>
       </c>
       <c r="E93">
-        <v>49.51299999999999</v>
+        <v>50.35599999999999</v>
       </c>
       <c r="F93">
-        <v>76.71299999999999</v>
+        <v>77.556</v>
       </c>
       <c r="G93">
         <v>17.7</v>
@@ -8913,28 +8913,28 @@
         <v>154.1</v>
       </c>
       <c r="M93">
-        <v>3.858663899999999</v>
+        <v>3.9010668</v>
       </c>
       <c r="N93">
-        <v>150.2413361</v>
+        <v>150.1989332</v>
       </c>
       <c r="O93">
-        <v>52.58446763499999</v>
+        <v>52.56962661999999</v>
       </c>
       <c r="P93">
-        <v>97.656868465</v>
+        <v>97.62930658000001</v>
       </c>
       <c r="Q93">
-        <v>112.256868465</v>
+        <v>112.22930658</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.9014593166512057</v>
+        <v>1.003472991600451</v>
       </c>
       <c r="T93">
-        <v>5.233105864127145</v>
+        <v>5.857008800972826</v>
       </c>
       <c r="U93">
         <v>0.0503</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>39.93610327139402</v>
+        <v>39.50201519235713</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1103572393280361</v>
+        <v>0.1098306901574636</v>
       </c>
       <c r="C94">
-        <v>12.75475735212041</v>
+        <v>11.97852735058855</v>
       </c>
       <c r="D94">
-        <v>72.6107573521204</v>
+        <v>72.67752735058855</v>
       </c>
       <c r="E94">
-        <v>50.35599999999999</v>
+        <v>51.199</v>
       </c>
       <c r="F94">
-        <v>77.556</v>
+        <v>78.399</v>
       </c>
       <c r="G94">
         <v>17.7</v>
@@ -8995,28 +8995,28 @@
         <v>154.1</v>
       </c>
       <c r="M94">
-        <v>3.9010668</v>
+        <v>3.9434697</v>
       </c>
       <c r="N94">
-        <v>150.1989332</v>
+        <v>150.1565303</v>
       </c>
       <c r="O94">
-        <v>52.56962661999999</v>
+        <v>52.55478560499999</v>
       </c>
       <c r="P94">
-        <v>97.62930658000001</v>
+        <v>97.60174469499999</v>
       </c>
       <c r="Q94">
-        <v>112.22930658</v>
+        <v>112.201744695</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.003472991600451</v>
+        <v>1.134633430820909</v>
       </c>
       <c r="T94">
-        <v>5.857008800972826</v>
+        <v>6.659169719774414</v>
       </c>
       <c r="U94">
         <v>0.0503</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>39.50201519235713</v>
+        <v>39.07726234082641</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1098306901574636</v>
+        <v>0.1093041409868911</v>
       </c>
       <c r="C95">
-        <v>11.97852735058855</v>
+        <v>11.20242026021332</v>
       </c>
       <c r="D95">
-        <v>72.67752735058855</v>
+        <v>72.74442026021332</v>
       </c>
       <c r="E95">
-        <v>51.199</v>
+        <v>52.042</v>
       </c>
       <c r="F95">
-        <v>78.399</v>
+        <v>79.242</v>
       </c>
       <c r="G95">
         <v>17.7</v>
@@ -9077,28 +9077,28 @@
         <v>154.1</v>
       </c>
       <c r="M95">
-        <v>3.9434697</v>
+        <v>3.9858726</v>
       </c>
       <c r="N95">
-        <v>150.1565303</v>
+        <v>150.1141274</v>
       </c>
       <c r="O95">
-        <v>52.55478560499999</v>
+        <v>52.53994459</v>
       </c>
       <c r="P95">
-        <v>97.60174469499999</v>
+        <v>97.57418281</v>
       </c>
       <c r="Q95">
-        <v>112.201744695</v>
+        <v>112.17418281</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.134633430820909</v>
+        <v>1.309514016448187</v>
       </c>
       <c r="T95">
-        <v>6.659169719774414</v>
+        <v>7.728717611509867</v>
       </c>
       <c r="U95">
         <v>0.0503</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>39.07726234082641</v>
+        <v>38.6615467840091</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1093041409868911</v>
+        <v>0.1087775918163187</v>
       </c>
       <c r="C96">
-        <v>11.20242026021332</v>
+        <v>10.42643642069224</v>
       </c>
       <c r="D96">
-        <v>72.74442026021332</v>
+        <v>72.81143642069225</v>
       </c>
       <c r="E96">
-        <v>52.042</v>
+        <v>52.88500000000001</v>
       </c>
       <c r="F96">
-        <v>79.242</v>
+        <v>80.08500000000001</v>
       </c>
       <c r="G96">
         <v>17.7</v>
@@ -9159,28 +9159,28 @@
         <v>154.1</v>
       </c>
       <c r="M96">
-        <v>3.9858726</v>
+        <v>4.0282755</v>
       </c>
       <c r="N96">
-        <v>150.1141274</v>
+        <v>150.0717245</v>
       </c>
       <c r="O96">
-        <v>52.53994459</v>
+        <v>52.525103575</v>
       </c>
       <c r="P96">
-        <v>97.57418281</v>
+        <v>97.54662092499998</v>
       </c>
       <c r="Q96">
-        <v>112.17418281</v>
+        <v>112.146620925</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.309514016448187</v>
+        <v>1.554346836326376</v>
       </c>
       <c r="T96">
-        <v>7.728717611509867</v>
+        <v>9.226084659939504</v>
       </c>
       <c r="U96">
         <v>0.0503</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>38.6615467840091</v>
+        <v>38.2545831336511</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1087775918163187</v>
+        <v>0.1082510426457462</v>
       </c>
       <c r="C97">
-        <v>10.42643642069224</v>
+        <v>9.650576172975846</v>
       </c>
       <c r="D97">
-        <v>72.81143642069225</v>
+        <v>72.87857617297584</v>
       </c>
       <c r="E97">
-        <v>52.88500000000001</v>
+        <v>53.72799999999999</v>
       </c>
       <c r="F97">
-        <v>80.08500000000001</v>
+        <v>80.928</v>
       </c>
       <c r="G97">
         <v>17.7</v>
@@ -9241,28 +9241,28 @@
         <v>154.1</v>
       </c>
       <c r="M97">
-        <v>4.0282755</v>
+        <v>4.070678399999999</v>
       </c>
       <c r="N97">
-        <v>150.0717245</v>
+        <v>150.0293216</v>
       </c>
       <c r="O97">
-        <v>52.525103575</v>
+        <v>52.51026256</v>
       </c>
       <c r="P97">
-        <v>97.54662092499998</v>
+        <v>97.51905904</v>
       </c>
       <c r="Q97">
-        <v>112.146620925</v>
+        <v>112.11905904</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.554346836326376</v>
+        <v>1.921596066143659</v>
       </c>
       <c r="T97">
-        <v>9.226084659939504</v>
+        <v>11.47213523258396</v>
       </c>
       <c r="U97">
         <v>0.0503</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>38.2545831336511</v>
+        <v>37.85609789267559</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1082510426457462</v>
+        <v>0.1077244934751738</v>
       </c>
       <c r="C98">
-        <v>9.650576172975832</v>
+        <v>8.874839859273308</v>
       </c>
       <c r="D98">
-        <v>72.87857617297583</v>
+        <v>72.94583985927331</v>
       </c>
       <c r="E98">
-        <v>53.72799999999999</v>
+        <v>54.571</v>
       </c>
       <c r="F98">
-        <v>80.928</v>
+        <v>81.771</v>
       </c>
       <c r="G98">
         <v>17.7</v>
@@ -9323,28 +9323,28 @@
         <v>154.1</v>
       </c>
       <c r="M98">
-        <v>4.070678399999999</v>
+        <v>4.1130813</v>
       </c>
       <c r="N98">
-        <v>150.0293216</v>
+        <v>149.9869187</v>
       </c>
       <c r="O98">
-        <v>52.51026256</v>
+        <v>52.49542154499999</v>
       </c>
       <c r="P98">
-        <v>97.51905904</v>
+        <v>97.49149715499999</v>
       </c>
       <c r="Q98">
-        <v>112.11905904</v>
+        <v>112.091497155</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.921596066143654</v>
+        <v>2.533678115839123</v>
       </c>
       <c r="T98">
-        <v>11.47213523258393</v>
+        <v>15.215552853658</v>
       </c>
       <c r="U98">
         <v>0.0503</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>37.85609789267559</v>
+        <v>37.46582884223562</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1077244934751738</v>
+        <v>0.1071979443046013</v>
       </c>
       <c r="C99">
-        <v>8.874839859273308</v>
+        <v>8.099227823058442</v>
       </c>
       <c r="D99">
-        <v>72.94583985927331</v>
+        <v>73.01322782305843</v>
       </c>
       <c r="E99">
-        <v>54.571</v>
+        <v>55.41399999999999</v>
       </c>
       <c r="F99">
-        <v>81.771</v>
+        <v>82.61399999999999</v>
       </c>
       <c r="G99">
         <v>17.7</v>
@@ -9405,28 +9405,28 @@
         <v>154.1</v>
       </c>
       <c r="M99">
-        <v>4.1130813</v>
+        <v>4.155484199999999</v>
       </c>
       <c r="N99">
-        <v>149.9869187</v>
+        <v>149.9445158</v>
       </c>
       <c r="O99">
-        <v>52.49542154499999</v>
+        <v>52.48058053</v>
       </c>
       <c r="P99">
-        <v>97.49149715499999</v>
+        <v>97.46393527000001</v>
       </c>
       <c r="Q99">
-        <v>112.091497155</v>
+        <v>112.06393527</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.533678115839123</v>
+        <v>3.757842215230061</v>
       </c>
       <c r="T99">
-        <v>15.215552853658</v>
+        <v>22.70238809580614</v>
       </c>
       <c r="U99">
         <v>0.0503</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>37.46582884223562</v>
+        <v>37.08352446629446</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1071979443046013</v>
+        <v>0.1066713951340288</v>
       </c>
       <c r="C100">
-        <v>8.099227823058442</v>
+        <v>7.32374040907537</v>
       </c>
       <c r="D100">
-        <v>73.01322782305843</v>
+        <v>73.08074040907536</v>
       </c>
       <c r="E100">
-        <v>55.41399999999999</v>
+        <v>56.25699999999999</v>
       </c>
       <c r="F100">
-        <v>82.61399999999999</v>
+        <v>83.45699999999999</v>
       </c>
       <c r="G100">
         <v>17.7</v>
@@ -9487,28 +9487,28 @@
         <v>154.1</v>
       </c>
       <c r="M100">
-        <v>4.155484199999999</v>
+        <v>4.197887099999999</v>
       </c>
       <c r="N100">
-        <v>149.9445158</v>
+        <v>149.9021129</v>
       </c>
       <c r="O100">
-        <v>52.48058053</v>
+        <v>52.465739515</v>
       </c>
       <c r="P100">
-        <v>97.46393527000001</v>
+        <v>97.436373385</v>
       </c>
       <c r="Q100">
-        <v>112.06393527</v>
+        <v>112.036373385</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.757842215230061</v>
+        <v>7.430334513402878</v>
       </c>
       <c r="T100">
-        <v>22.70238809580614</v>
+        <v>45.16289382225058</v>
       </c>
       <c r="U100">
         <v>0.0503</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>37.08352446629446</v>
+        <v>36.70894341107935</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1066713951340288</v>
-      </c>
-      <c r="C101">
-        <v>7.32374040907537</v>
-      </c>
-      <c r="D101">
-        <v>73.08074040907536</v>
-      </c>
-      <c r="E101">
-        <v>56.25699999999999</v>
-      </c>
-      <c r="F101">
-        <v>83.45699999999999</v>
-      </c>
-      <c r="G101">
-        <v>17.7</v>
-      </c>
-      <c r="H101">
-        <v>57.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>168.7</v>
-      </c>
-      <c r="K101">
-        <v>14.6</v>
-      </c>
-      <c r="L101">
-        <v>154.1</v>
-      </c>
-      <c r="M101">
-        <v>4.197887099999999</v>
-      </c>
-      <c r="N101">
-        <v>149.9021129</v>
-      </c>
-      <c r="O101">
-        <v>52.465739515</v>
-      </c>
-      <c r="P101">
-        <v>97.436373385</v>
-      </c>
-      <c r="Q101">
-        <v>112.036373385</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.430334513402878</v>
-      </c>
-      <c r="T101">
-        <v>45.16289382225058</v>
-      </c>
-      <c r="U101">
-        <v>0.0503</v>
-      </c>
-      <c r="V101">
-        <v>0.35</v>
-      </c>
-      <c r="W101">
-        <v>0.032695</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Aaa/AAA</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>36.70894341107935</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
